--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,338 +394,274 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>6262</v>
+        <v>5858</v>
       </c>
       <c r="B2" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>6217</v>
+        <v>5800</v>
       </c>
       <c r="B3" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>6168</v>
+        <v>5729</v>
       </c>
       <c r="B4" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>6113</v>
+        <v>5712</v>
       </c>
       <c r="B5" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>6125</v>
+        <v>5608</v>
       </c>
       <c r="B6" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>6048</v>
+        <v>5570</v>
       </c>
       <c r="B7" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>6031</v>
+        <v>5536</v>
       </c>
       <c r="B8" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5978</v>
+        <v>5540</v>
       </c>
       <c r="B9" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.03125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5929</v>
+        <v>5579</v>
       </c>
       <c r="B10" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.04166666666</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5912</v>
+        <v>5585</v>
       </c>
       <c r="B11" s="2">
-        <v>46079.0625</v>
+        <v>46094.05208333334</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5898</v>
+        <v>5574</v>
       </c>
       <c r="B12" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.0625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5886</v>
+        <v>5547</v>
       </c>
       <c r="B13" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.07291666666</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5895</v>
+        <v>5566</v>
       </c>
       <c r="B14" s="2">
-        <v>46079.09375</v>
+        <v>46094.08333333334</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5856</v>
+        <v>5540</v>
       </c>
       <c r="B15" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.09375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5925</v>
+        <v>5528</v>
       </c>
       <c r="B16" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.10416666666</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5924</v>
+        <v>5534</v>
       </c>
       <c r="B17" s="2">
-        <v>46079.125</v>
+        <v>46094.11458333334</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5955</v>
+        <v>5613</v>
       </c>
       <c r="B18" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5935</v>
+        <v>5614</v>
       </c>
       <c r="B19" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.13541666666</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5960</v>
+        <v>5636</v>
       </c>
       <c r="B20" s="2">
-        <v>46079.15625</v>
+        <v>46094.14583333334</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>6087</v>
+        <v>5662</v>
       </c>
       <c r="B21" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.15625</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>6137</v>
+        <v>5745</v>
       </c>
       <c r="B22" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.16666666666</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>6226</v>
+        <v>5827</v>
       </c>
       <c r="B23" s="2">
-        <v>46079.1875</v>
+        <v>46094.17708333334</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>6328</v>
+        <v>5934</v>
       </c>
       <c r="B24" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.1875</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6546</v>
+        <v>6070</v>
       </c>
       <c r="B25" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.19791666666</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6707</v>
+        <v>6101</v>
       </c>
       <c r="B26" s="2">
-        <v>46079.21875</v>
+        <v>46094.20833333334</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6791</v>
+        <v>6251</v>
       </c>
       <c r="B27" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.21875</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6971</v>
+        <v>6296</v>
       </c>
       <c r="B28" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.22916666666</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>7154</v>
+        <v>6420</v>
       </c>
       <c r="B29" s="2">
-        <v>46079.25</v>
+        <v>46094.23958333334</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>7393</v>
+        <v>6647</v>
       </c>
       <c r="B30" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.25</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>7498</v>
+        <v>6689</v>
       </c>
       <c r="B31" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.26041666666</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>7558</v>
+        <v>6671</v>
       </c>
       <c r="B32" s="2">
-        <v>46079.28125</v>
+        <v>46094.27083333334</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>7633</v>
+        <v>6630</v>
       </c>
       <c r="B33" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.28125</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>7648</v>
+        <v>6574</v>
       </c>
       <c r="B34" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.29166666666</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>7607</v>
+        <v>6526</v>
       </c>
       <c r="B35" s="2">
-        <v>46079.3125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>7569</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46079.32291666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>7562</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46079.33333333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>7518</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46079.34375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>7459</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46079.35416666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>7365</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46079.36458333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>7149</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46079.375</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>7015</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46079.38541666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>6910</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.30208333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -26,9 +26,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -81,12 +78,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -392,278 +388,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>5858</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46093.95833333334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>5800</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46093.96875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>5729</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46093.97916666666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>5712</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46093.98958333334</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5608</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>5570</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46094.01041666666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>5536</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46094.02083333334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>5540</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46094.03125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>5579</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46094.04166666666</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>5585</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46094.05208333334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>5574</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46094.0625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>5547</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46094.07291666666</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>5566</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46094.08333333334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>5540</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46094.09375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>5528</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46094.10416666666</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>5534</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46094.11458333334</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>5613</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46094.125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>5614</v>
-      </c>
-      <c r="B19" s="2">
-        <v>46094.13541666666</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>5636</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46094.14583333334</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>5662</v>
-      </c>
-      <c r="B21" s="2">
-        <v>46094.15625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>5745</v>
-      </c>
-      <c r="B22" s="2">
-        <v>46094.16666666666</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>5827</v>
-      </c>
-      <c r="B23" s="2">
-        <v>46094.17708333334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>5934</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46094.1875</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>6070</v>
-      </c>
-      <c r="B25" s="2">
-        <v>46094.19791666666</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>6101</v>
-      </c>
-      <c r="B26" s="2">
-        <v>46094.20833333334</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>6251</v>
-      </c>
-      <c r="B27" s="2">
-        <v>46094.21875</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>6296</v>
-      </c>
-      <c r="B28" s="2">
-        <v>46094.22916666666</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>6420</v>
-      </c>
-      <c r="B29" s="2">
-        <v>46094.23958333334</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>6647</v>
-      </c>
-      <c r="B30" s="2">
-        <v>46094.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>6689</v>
-      </c>
-      <c r="B31" s="2">
-        <v>46094.26041666666</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>6671</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46094.27083333334</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>6630</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46094.28125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>6574</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46094.29166666666</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>6526</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46094.30208333334</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -26,6 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -78,11 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +392,246 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>5172</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>5082</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46111.01041666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>5072</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46111.02083333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>5018</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46111.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5101</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46111.04166666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5035</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46111.05208333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>5075</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46111.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>5063</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46111.07291666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>5061</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46111.08333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>5003</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46111.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>4984</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46111.10416666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>5006</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46111.11458333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>5024</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46111.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>5043</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46111.13541666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>5012</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46111.14583333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>5041</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46111.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>5147</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46111.16666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>5229</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46111.17708333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>5348</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46111.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>5447</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46111.19791666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>5600</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46111.20833333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>5810</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46111.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>5954</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46111.22916666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>6162</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46111.23958333334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>6409</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46111.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>6592</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46111.26041666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>6724</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46111.27083333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>6881</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46111.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>7090</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46111.29166666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>7249</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46111.30208333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_7A71C53EB030921FD2FE31D2F8375B06E490DEF4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A076FF4-D54C-442E-A7B6-E3CC16ED9B26}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,244 +425,412 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5172</v>
+        <v>5690</v>
       </c>
       <c r="B2" s="2">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5082</v>
+        <v>5624</v>
       </c>
       <c r="B3" s="2">
-        <v>46111.01041666666</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>46115.010416666657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5072</v>
+        <v>5592</v>
       </c>
       <c r="B4" s="2">
-        <v>46111.02083333334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>46115.020833333343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5018</v>
+        <v>5553</v>
       </c>
       <c r="B5" s="2">
-        <v>46111.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>46115.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5101</v>
+        <v>5632</v>
       </c>
       <c r="B6" s="2">
-        <v>46111.04166666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>46115.041666666657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5035</v>
+        <v>5654</v>
       </c>
       <c r="B7" s="2">
-        <v>46111.05208333334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>46115.052083333343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5075</v>
+        <v>5606</v>
       </c>
       <c r="B8" s="2">
-        <v>46111.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>46115.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>5063</v>
+        <v>5565</v>
       </c>
       <c r="B9" s="2">
-        <v>46111.07291666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>46115.072916666657</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5061</v>
+        <v>5529</v>
       </c>
       <c r="B10" s="2">
-        <v>46111.08333333334</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>46115.083333333343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5003</v>
+        <v>5527</v>
       </c>
       <c r="B11" s="2">
-        <v>46111.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>46115.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4984</v>
+        <v>5561</v>
       </c>
       <c r="B12" s="2">
-        <v>46111.10416666666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>46115.104166666657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5006</v>
+        <v>5560</v>
       </c>
       <c r="B13" s="2">
-        <v>46111.11458333334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>46115.114583333343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5024</v>
+        <v>5555</v>
       </c>
       <c r="B14" s="2">
-        <v>46111.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>46115.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5043</v>
+        <v>5567</v>
       </c>
       <c r="B15" s="2">
-        <v>46111.13541666666</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>46115.135416666657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5012</v>
+        <v>5615</v>
       </c>
       <c r="B16" s="2">
-        <v>46111.14583333334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>46115.145833333343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5041</v>
+        <v>5633</v>
       </c>
       <c r="B17" s="2">
-        <v>46111.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>46115.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5147</v>
+        <v>5705</v>
       </c>
       <c r="B18" s="2">
-        <v>46111.16666666666</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>46115.166666666657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5229</v>
+        <v>5774</v>
       </c>
       <c r="B19" s="2">
-        <v>46111.17708333334</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>46115.177083333343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5348</v>
+        <v>5867</v>
       </c>
       <c r="B20" s="2">
-        <v>46111.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>46115.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5447</v>
+        <v>5918</v>
       </c>
       <c r="B21" s="2">
-        <v>46111.19791666666</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>46115.197916666657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5600</v>
+        <v>5979</v>
       </c>
       <c r="B22" s="2">
-        <v>46111.20833333334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>46115.208333333343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5810</v>
+        <v>6086</v>
       </c>
       <c r="B23" s="2">
-        <v>46111.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>46115.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>5954</v>
+        <v>6172</v>
       </c>
       <c r="B24" s="2">
-        <v>46111.22916666666</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>46115.229166666657</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>6162</v>
+        <v>6308</v>
       </c>
       <c r="B25" s="2">
-        <v>46111.23958333334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>46115.239583333343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>6409</v>
+        <v>6460</v>
       </c>
       <c r="B26" s="2">
-        <v>46111.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>46115.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>6592</v>
+        <v>6628</v>
       </c>
       <c r="B27" s="2">
-        <v>46111.26041666666</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>46115.260416666657</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>6724</v>
+        <v>6771</v>
       </c>
       <c r="B28" s="2">
-        <v>46111.27083333334</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>46115.270833333343</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>6881</v>
+        <v>6908</v>
       </c>
       <c r="B29" s="2">
-        <v>46111.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>46115.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>7090</v>
+        <v>7120</v>
       </c>
       <c r="B30" s="2">
-        <v>46111.29166666666</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>46115.291666666657</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>7249</v>
+        <v>7209</v>
       </c>
       <c r="B31" s="2">
-        <v>46111.30208333334</v>
+        <v>46115.302083333343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>7244</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46115.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7288</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46115.322916666657</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7259</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46115.333333333343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7219</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46115.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7197</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46115.354166666657</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>7199</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46115.364583333343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>7105</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46115.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>7010</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46115.385416666657</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>6956</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46115.395833333343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>6900</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46115.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>6736</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46115.416666666657</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>6641</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46115.427083333343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>6612</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46115.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>6512</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46115.447916666657</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>6494</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46115.458333333343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>6405</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46115.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>6517</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46115.479166666657</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>6388</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46115.489583333343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>6238</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46115.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>6192</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46115.510416666657</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>6164</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46115.520833333343</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_7A71C53EB030921FD2FE31D2F8375B06E490DEF4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A076FF4-D54C-442E-A7B6-E3CC16ED9B26}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,412 +392,388 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>5690</v>
+        <v>5273</v>
       </c>
       <c r="B2" s="2">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
-        <v>5624</v>
+        <v>5261</v>
       </c>
       <c r="B3" s="2">
-        <v>46115.010416666657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.01041666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
-        <v>5592</v>
+        <v>5164</v>
       </c>
       <c r="B4" s="2">
-        <v>46115.020833333343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.02083333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
-        <v>5553</v>
+        <v>5196</v>
       </c>
       <c r="B5" s="2">
-        <v>46115.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
-        <v>5632</v>
+        <v>5246</v>
       </c>
       <c r="B6" s="2">
-        <v>46115.041666666657</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.04166666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>5654</v>
+        <v>5257</v>
       </c>
       <c r="B7" s="2">
-        <v>46115.052083333343</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.05208333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
-        <v>5606</v>
+        <v>5211</v>
       </c>
       <c r="B8" s="2">
-        <v>46115.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
-        <v>5565</v>
+        <v>5182</v>
       </c>
       <c r="B9" s="2">
-        <v>46115.072916666657</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.07291666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
-        <v>5529</v>
+        <v>5193</v>
       </c>
       <c r="B10" s="2">
-        <v>46115.083333333343</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.08333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
-        <v>5527</v>
+        <v>5166</v>
       </c>
       <c r="B11" s="2">
-        <v>46115.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>5561</v>
+        <v>5192</v>
       </c>
       <c r="B12" s="2">
-        <v>46115.104166666657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.10416666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
-        <v>5560</v>
+        <v>5200</v>
       </c>
       <c r="B13" s="2">
-        <v>46115.114583333343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.11458333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>5555</v>
+        <v>5193</v>
       </c>
       <c r="B14" s="2">
-        <v>46115.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
-        <v>5567</v>
+        <v>5179</v>
       </c>
       <c r="B15" s="2">
-        <v>46115.135416666657</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.13541666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
-        <v>5615</v>
+        <v>5208</v>
       </c>
       <c r="B16" s="2">
-        <v>46115.145833333343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.14583333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>5633</v>
+        <v>5272</v>
       </c>
       <c r="B17" s="2">
-        <v>46115.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
-        <v>5705</v>
+        <v>5309</v>
       </c>
       <c r="B18" s="2">
-        <v>46115.166666666657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.16666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
-        <v>5774</v>
+        <v>5322</v>
       </c>
       <c r="B19" s="2">
-        <v>46115.177083333343</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.17708333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
-        <v>5867</v>
+        <v>5408</v>
       </c>
       <c r="B20" s="2">
-        <v>46115.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
-        <v>5918</v>
+        <v>5504</v>
       </c>
       <c r="B21" s="2">
-        <v>46115.197916666657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.19791666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>5979</v>
+        <v>5541</v>
       </c>
       <c r="B22" s="2">
-        <v>46115.208333333343</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.20833333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
-        <v>6086</v>
+        <v>5646</v>
       </c>
       <c r="B23" s="2">
-        <v>46115.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
-        <v>6172</v>
+        <v>5675</v>
       </c>
       <c r="B24" s="2">
-        <v>46115.229166666657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.22916666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
-        <v>6308</v>
+        <v>5801</v>
       </c>
       <c r="B25" s="2">
-        <v>46115.239583333343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.23958333334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
-        <v>6460</v>
+        <v>6041</v>
       </c>
       <c r="B26" s="2">
-        <v>46115.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>6628</v>
+        <v>6216</v>
       </c>
       <c r="B27" s="2">
-        <v>46115.260416666657</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.26041666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
-        <v>6771</v>
+        <v>6119</v>
       </c>
       <c r="B28" s="2">
-        <v>46115.270833333343</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.27083333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
-        <v>6908</v>
+        <v>6140</v>
       </c>
       <c r="B29" s="2">
-        <v>46115.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
-        <v>7120</v>
+        <v>5946</v>
       </c>
       <c r="B30" s="2">
-        <v>46115.291666666657</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.29166666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
-        <v>7209</v>
+        <v>6182</v>
       </c>
       <c r="B31" s="2">
-        <v>46115.302083333343</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>7244</v>
+        <v>6075</v>
       </c>
       <c r="B32" s="2">
-        <v>46115.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
-        <v>7288</v>
+        <v>6042</v>
       </c>
       <c r="B33" s="2">
-        <v>46115.322916666657</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
-        <v>7259</v>
+        <v>5988</v>
       </c>
       <c r="B34" s="2">
-        <v>46115.333333333343</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
-        <v>7219</v>
+        <v>5949</v>
       </c>
       <c r="B35" s="2">
-        <v>46115.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
-        <v>7197</v>
+        <v>5760</v>
       </c>
       <c r="B36" s="2">
-        <v>46115.354166666657</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
-        <v>7199</v>
+        <v>5682</v>
       </c>
       <c r="B37" s="2">
-        <v>46115.364583333343</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
-        <v>7105</v>
+        <v>5476</v>
       </c>
       <c r="B38" s="2">
-        <v>46115.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
-        <v>7010</v>
+        <v>5369</v>
       </c>
       <c r="B39" s="2">
-        <v>46115.385416666657</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
-        <v>6956</v>
+        <v>5205</v>
       </c>
       <c r="B40" s="2">
-        <v>46115.395833333343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
-        <v>6900</v>
+        <v>5101</v>
       </c>
       <c r="B41" s="2">
-        <v>46115.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
-        <v>6736</v>
+        <v>4911</v>
       </c>
       <c r="B42" s="2">
-        <v>46115.416666666657</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
-        <v>6641</v>
+        <v>4801</v>
       </c>
       <c r="B43" s="2">
-        <v>46115.427083333343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
-        <v>6612</v>
+        <v>4778</v>
       </c>
       <c r="B44" s="2">
-        <v>46115.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
-        <v>6512</v>
+        <v>4749</v>
       </c>
       <c r="B45" s="2">
-        <v>46115.447916666657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
-        <v>6494</v>
+        <v>4798</v>
       </c>
       <c r="B46" s="2">
-        <v>46115.458333333343</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
-        <v>6405</v>
+        <v>4794</v>
       </c>
       <c r="B47" s="2">
-        <v>46115.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
-        <v>6517</v>
+        <v>4708</v>
       </c>
       <c r="B48" s="2">
-        <v>46115.479166666657</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46129.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49">
-        <v>6388</v>
+        <v>4700</v>
       </c>
       <c r="B49" s="2">
-        <v>46115.489583333343</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>6238</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46115.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>6192</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46115.510416666657</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>6164</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46115.520833333343</v>
+        <v>46129.48958333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,386 +394,242 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5273</v>
+        <v>4827</v>
       </c>
       <c r="B2" s="2">
-        <v>46129</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5261</v>
+        <v>4752</v>
       </c>
       <c r="B3" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5164</v>
+        <v>4717</v>
       </c>
       <c r="B4" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5196</v>
+        <v>4727</v>
       </c>
       <c r="B5" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5246</v>
+        <v>4706</v>
       </c>
       <c r="B6" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5257</v>
+        <v>4690</v>
       </c>
       <c r="B7" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.0625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5211</v>
+        <v>4649</v>
       </c>
       <c r="B8" s="2">
-        <v>46129.0625</v>
+        <v>46132.07291666666</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5182</v>
+        <v>4636</v>
       </c>
       <c r="B9" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.08333333334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5193</v>
+        <v>4671</v>
       </c>
       <c r="B10" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.09375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5166</v>
+        <v>4578</v>
       </c>
       <c r="B11" s="2">
-        <v>46129.09375</v>
+        <v>46132.10416666666</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5192</v>
+        <v>4572</v>
       </c>
       <c r="B12" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.11458333334</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5200</v>
+        <v>4582</v>
       </c>
       <c r="B13" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5193</v>
+        <v>4595</v>
       </c>
       <c r="B14" s="2">
-        <v>46129.125</v>
+        <v>46132.13541666666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5179</v>
+        <v>4676</v>
       </c>
       <c r="B15" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.14583333334</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5208</v>
+        <v>4711</v>
       </c>
       <c r="B16" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.15625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5272</v>
+        <v>4840</v>
       </c>
       <c r="B17" s="2">
-        <v>46129.15625</v>
+        <v>46132.16666666666</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5309</v>
+        <v>4858</v>
       </c>
       <c r="B18" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.17708333334</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5322</v>
+        <v>5067</v>
       </c>
       <c r="B19" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.19791666666</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5408</v>
+        <v>5141</v>
       </c>
       <c r="B20" s="2">
-        <v>46129.1875</v>
+        <v>46132.20833333334</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5504</v>
+        <v>5344</v>
       </c>
       <c r="B21" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.21875</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5541</v>
+        <v>5454</v>
       </c>
       <c r="B22" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.22916666666</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5646</v>
+        <v>5652</v>
       </c>
       <c r="B23" s="2">
-        <v>46129.21875</v>
+        <v>46132.23958333334</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5675</v>
+        <v>5846</v>
       </c>
       <c r="B24" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.25</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5801</v>
+        <v>5946</v>
       </c>
       <c r="B25" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.26041666666</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6041</v>
+        <v>6028</v>
       </c>
       <c r="B26" s="2">
-        <v>46129.25</v>
+        <v>46132.27083333334</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6216</v>
+        <v>6060</v>
       </c>
       <c r="B27" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.28125</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6119</v>
+        <v>6135</v>
       </c>
       <c r="B28" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.29166666666</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6140</v>
+        <v>6216</v>
       </c>
       <c r="B29" s="2">
-        <v>46129.28125</v>
+        <v>46132.30208333334</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5946</v>
+        <v>6192</v>
       </c>
       <c r="B30" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.3125</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6182</v>
+        <v>6058</v>
       </c>
       <c r="B31" s="2">
-        <v>46129.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>6075</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46129.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>6042</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46129.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>5988</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46129.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>5949</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46129.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>5760</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46129.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>5682</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46129.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>5476</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46129.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>5369</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46129.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>5205</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46129.39583333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>5101</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46129.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>4911</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46129.41666666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>4801</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46129.42708333334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>4778</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46129.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>4749</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46129.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>4798</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46129.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>4794</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46129.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>4708</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46129.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>4700</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.32291666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,242 +394,322 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4827</v>
+        <v>5156</v>
       </c>
       <c r="B2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4752</v>
+        <v>5120</v>
       </c>
       <c r="B3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4717</v>
+        <v>5163</v>
       </c>
       <c r="B4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4727</v>
+        <v>5220</v>
       </c>
       <c r="B5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4706</v>
+        <v>5273</v>
       </c>
       <c r="B6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4690</v>
+        <v>5132</v>
       </c>
       <c r="B7" s="2">
-        <v>46132.0625</v>
+        <v>46133.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4649</v>
+        <v>5283</v>
       </c>
       <c r="B8" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4636</v>
+        <v>5213</v>
       </c>
       <c r="B9" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4671</v>
+        <v>5058</v>
       </c>
       <c r="B10" s="2">
-        <v>46132.09375</v>
+        <v>46133.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4578</v>
+        <v>5141</v>
       </c>
       <c r="B11" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4572</v>
+        <v>5066</v>
       </c>
       <c r="B12" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4582</v>
+        <v>5048</v>
       </c>
       <c r="B13" s="2">
-        <v>46132.125</v>
+        <v>46133.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4595</v>
+        <v>5025</v>
       </c>
       <c r="B14" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4676</v>
+        <v>5023</v>
       </c>
       <c r="B15" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4711</v>
+        <v>5063</v>
       </c>
       <c r="B16" s="2">
-        <v>46132.15625</v>
+        <v>46133.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4840</v>
+        <v>5104</v>
       </c>
       <c r="B17" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4858</v>
+        <v>5131</v>
       </c>
       <c r="B18" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5067</v>
+        <v>5221</v>
       </c>
       <c r="B19" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5141</v>
+        <v>5304</v>
       </c>
       <c r="B20" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5344</v>
+        <v>5353</v>
       </c>
       <c r="B21" s="2">
-        <v>46132.21875</v>
+        <v>46133.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5454</v>
+        <v>5556</v>
       </c>
       <c r="B22" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5652</v>
+        <v>5629</v>
       </c>
       <c r="B23" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5846</v>
+        <v>5691</v>
       </c>
       <c r="B24" s="2">
-        <v>46132.25</v>
+        <v>46133.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5946</v>
+        <v>5823</v>
       </c>
       <c r="B25" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6028</v>
+        <v>6057</v>
       </c>
       <c r="B26" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6060</v>
+        <v>6215</v>
       </c>
       <c r="B27" s="2">
-        <v>46132.28125</v>
+        <v>46133.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6135</v>
+        <v>6269</v>
       </c>
       <c r="B28" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6216</v>
+        <v>6321</v>
       </c>
       <c r="B29" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6192</v>
+        <v>6391</v>
       </c>
       <c r="B30" s="2">
-        <v>46132.3125</v>
+        <v>46133.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6058</v>
+        <v>6497</v>
       </c>
       <c r="B31" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>6474</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46133.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>6434</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46133.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>6480</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46133.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>6371</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46133.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>6332</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46133.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>6222</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46133.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>6108</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46133.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>6068</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46133.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>5930</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46133.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>5848</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46133.40625</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,322 +394,370 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5156</v>
+        <v>4796</v>
       </c>
       <c r="B2" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5120</v>
+        <v>4722</v>
       </c>
       <c r="B3" s="2">
-        <v>46133.01041666666</v>
+        <v>46139.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5163</v>
+        <v>4754</v>
       </c>
       <c r="B4" s="2">
-        <v>46133.02083333334</v>
+        <v>46139.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5220</v>
+        <v>4712</v>
       </c>
       <c r="B5" s="2">
-        <v>46133.03125</v>
+        <v>46139.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5273</v>
+        <v>4752</v>
       </c>
       <c r="B6" s="2">
-        <v>46133.04166666666</v>
+        <v>46139.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5132</v>
+        <v>4742</v>
       </c>
       <c r="B7" s="2">
-        <v>46133.05208333334</v>
+        <v>46139.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5283</v>
+        <v>4691</v>
       </c>
       <c r="B8" s="2">
-        <v>46133.0625</v>
+        <v>46139.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5213</v>
+        <v>4718</v>
       </c>
       <c r="B9" s="2">
-        <v>46133.07291666666</v>
+        <v>46139.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5058</v>
+        <v>4799</v>
       </c>
       <c r="B10" s="2">
-        <v>46133.08333333334</v>
+        <v>46139.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5141</v>
+        <v>4807</v>
       </c>
       <c r="B11" s="2">
-        <v>46133.09375</v>
+        <v>46139.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5066</v>
+        <v>4722</v>
       </c>
       <c r="B12" s="2">
-        <v>46133.10416666666</v>
+        <v>46139.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5048</v>
+        <v>4745</v>
       </c>
       <c r="B13" s="2">
-        <v>46133.11458333334</v>
+        <v>46139.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5025</v>
+        <v>4758</v>
       </c>
       <c r="B14" s="2">
-        <v>46133.125</v>
+        <v>46139.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5023</v>
+        <v>4735</v>
       </c>
       <c r="B15" s="2">
-        <v>46133.13541666666</v>
+        <v>46139.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5063</v>
+        <v>4666</v>
       </c>
       <c r="B16" s="2">
-        <v>46133.14583333334</v>
+        <v>46139.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5104</v>
+        <v>4689</v>
       </c>
       <c r="B17" s="2">
-        <v>46133.15625</v>
+        <v>46139.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5131</v>
+        <v>4782</v>
       </c>
       <c r="B18" s="2">
-        <v>46133.16666666666</v>
+        <v>46139.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5221</v>
+        <v>4839</v>
       </c>
       <c r="B19" s="2">
-        <v>46133.17708333334</v>
+        <v>46139.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5304</v>
+        <v>4929</v>
       </c>
       <c r="B20" s="2">
-        <v>46133.1875</v>
+        <v>46139.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5353</v>
+        <v>5025</v>
       </c>
       <c r="B21" s="2">
-        <v>46133.19791666666</v>
+        <v>46139.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5556</v>
+        <v>5223</v>
       </c>
       <c r="B22" s="2">
-        <v>46133.20833333334</v>
+        <v>46139.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5629</v>
+        <v>5336</v>
       </c>
       <c r="B23" s="2">
-        <v>46133.21875</v>
+        <v>46139.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5691</v>
+        <v>5468</v>
       </c>
       <c r="B24" s="2">
-        <v>46133.22916666666</v>
+        <v>46139.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5823</v>
+        <v>5622</v>
       </c>
       <c r="B25" s="2">
-        <v>46133.23958333334</v>
+        <v>46139.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6057</v>
+        <v>5856</v>
       </c>
       <c r="B26" s="2">
-        <v>46133.25</v>
+        <v>46139.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6215</v>
+        <v>5967</v>
       </c>
       <c r="B27" s="2">
-        <v>46133.26041666666</v>
+        <v>46139.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6269</v>
+        <v>5969</v>
       </c>
       <c r="B28" s="2">
-        <v>46133.27083333334</v>
+        <v>46139.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6321</v>
+        <v>5985</v>
       </c>
       <c r="B29" s="2">
-        <v>46133.28125</v>
+        <v>46139.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6391</v>
+        <v>6071</v>
       </c>
       <c r="B30" s="2">
-        <v>46133.29166666666</v>
+        <v>46139.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6497</v>
+        <v>6032</v>
       </c>
       <c r="B31" s="2">
-        <v>46133.30208333334</v>
+        <v>46139.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6474</v>
+        <v>5947</v>
       </c>
       <c r="B32" s="2">
-        <v>46133.3125</v>
+        <v>46139.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6434</v>
+        <v>5757</v>
       </c>
       <c r="B33" s="2">
-        <v>46133.32291666666</v>
+        <v>46139.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6480</v>
+        <v>5571</v>
       </c>
       <c r="B34" s="2">
-        <v>46133.33333333334</v>
+        <v>46139.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6371</v>
+        <v>5425</v>
       </c>
       <c r="B35" s="2">
-        <v>46133.34375</v>
+        <v>46139.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6332</v>
+        <v>5187</v>
       </c>
       <c r="B36" s="2">
-        <v>46133.35416666666</v>
+        <v>46139.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>6222</v>
+        <v>5075</v>
       </c>
       <c r="B37" s="2">
-        <v>46133.36458333334</v>
+        <v>46139.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>6108</v>
+        <v>4876</v>
       </c>
       <c r="B38" s="2">
-        <v>46133.375</v>
+        <v>46139.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>6068</v>
+        <v>4765</v>
       </c>
       <c r="B39" s="2">
-        <v>46133.38541666666</v>
+        <v>46139.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>5930</v>
+        <v>4560</v>
       </c>
       <c r="B40" s="2">
-        <v>46133.39583333334</v>
+        <v>46139.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>5848</v>
+        <v>4442</v>
       </c>
       <c r="B41" s="2">
-        <v>46133.40625</v>
+        <v>46139.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>4349</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46139.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>4153</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46139.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>4053</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46139.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>3989</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46139.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>4008</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46139.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>4118</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46139.46875</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,370 +394,362 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4796</v>
+        <v>5379</v>
       </c>
       <c r="B2" s="2">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4722</v>
+        <v>5308</v>
       </c>
       <c r="B3" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4754</v>
+        <v>5299</v>
       </c>
       <c r="B4" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4712</v>
+        <v>5318</v>
       </c>
       <c r="B5" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4752</v>
+        <v>5260</v>
       </c>
       <c r="B6" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.05208333334</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4742</v>
+        <v>5279</v>
       </c>
       <c r="B7" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.0625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4691</v>
+        <v>5241</v>
       </c>
       <c r="B8" s="2">
-        <v>46139.0625</v>
+        <v>46142.07291666666</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4718</v>
+        <v>5021</v>
       </c>
       <c r="B9" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.08333333334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4799</v>
+        <v>4859</v>
       </c>
       <c r="B10" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.09375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4807</v>
+        <v>4872</v>
       </c>
       <c r="B11" s="2">
-        <v>46139.09375</v>
+        <v>46142.10416666666</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4722</v>
+        <v>4867</v>
       </c>
       <c r="B12" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.11458333334</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4745</v>
+        <v>4837</v>
       </c>
       <c r="B13" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4758</v>
+        <v>4872</v>
       </c>
       <c r="B14" s="2">
-        <v>46139.125</v>
+        <v>46142.13541666666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4735</v>
+        <v>4930</v>
       </c>
       <c r="B15" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.14583333334</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4666</v>
+        <v>4865</v>
       </c>
       <c r="B16" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.15625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4689</v>
+        <v>4874</v>
       </c>
       <c r="B17" s="2">
-        <v>46139.15625</v>
+        <v>46142.16666666666</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4782</v>
+        <v>5437</v>
       </c>
       <c r="B18" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.17708333334</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4839</v>
+        <v>5576</v>
       </c>
       <c r="B19" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.1875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4929</v>
+        <v>5596</v>
       </c>
       <c r="B20" s="2">
-        <v>46139.1875</v>
+        <v>46142.19791666666</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5025</v>
+        <v>5609</v>
       </c>
       <c r="B21" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.20833333334</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5223</v>
+        <v>5724</v>
       </c>
       <c r="B22" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.21875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5336</v>
+        <v>5907</v>
       </c>
       <c r="B23" s="2">
-        <v>46139.21875</v>
+        <v>46142.22916666666</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5468</v>
+        <v>6050</v>
       </c>
       <c r="B24" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.23958333334</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5622</v>
+        <v>6319</v>
       </c>
       <c r="B25" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5856</v>
+        <v>6425</v>
       </c>
       <c r="B26" s="2">
-        <v>46139.25</v>
+        <v>46142.26041666666</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5967</v>
+        <v>6508</v>
       </c>
       <c r="B27" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.27083333334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5969</v>
+        <v>6573</v>
       </c>
       <c r="B28" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.28125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5985</v>
+        <v>6712</v>
       </c>
       <c r="B29" s="2">
-        <v>46139.28125</v>
+        <v>46142.29166666666</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6071</v>
+        <v>6887</v>
       </c>
       <c r="B30" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.30208333334</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6032</v>
+        <v>6879</v>
       </c>
       <c r="B31" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.3125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5947</v>
+        <v>6788</v>
       </c>
       <c r="B32" s="2">
-        <v>46139.3125</v>
+        <v>46142.32291666666</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5757</v>
+        <v>6738</v>
       </c>
       <c r="B33" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.33333333334</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5571</v>
+        <v>6813</v>
       </c>
       <c r="B34" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.34375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5425</v>
+        <v>6723</v>
       </c>
       <c r="B35" s="2">
-        <v>46139.34375</v>
+        <v>46142.35416666666</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5187</v>
+        <v>6650</v>
       </c>
       <c r="B36" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.36458333334</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5075</v>
+        <v>6630</v>
       </c>
       <c r="B37" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>4876</v>
+        <v>6540</v>
       </c>
       <c r="B38" s="2">
-        <v>46139.375</v>
+        <v>46142.38541666666</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>4765</v>
+        <v>6409</v>
       </c>
       <c r="B39" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.39583333334</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>4560</v>
+        <v>6429</v>
       </c>
       <c r="B40" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.40625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>4442</v>
+        <v>6245</v>
       </c>
       <c r="B41" s="2">
-        <v>46139.40625</v>
+        <v>46142.41666666666</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>4349</v>
+        <v>6260</v>
       </c>
       <c r="B42" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.42708333334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>4153</v>
+        <v>6170</v>
       </c>
       <c r="B43" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.4375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>4053</v>
+        <v>6093</v>
       </c>
       <c r="B44" s="2">
-        <v>46139.4375</v>
+        <v>46142.44791666666</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>3989</v>
+        <v>6089</v>
       </c>
       <c r="B45" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.45833333334</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>4008</v>
+        <v>6135</v>
       </c>
       <c r="B46" s="2">
-        <v>46139.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>4118</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,362 +394,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5379</v>
+        <v>4898</v>
       </c>
       <c r="B2" s="2">
-        <v>46142</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5308</v>
+        <v>4875</v>
       </c>
       <c r="B3" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5299</v>
+        <v>4816</v>
       </c>
       <c r="B4" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5318</v>
+        <v>4740</v>
       </c>
       <c r="B5" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5260</v>
+        <v>4743</v>
       </c>
       <c r="B6" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5279</v>
+        <v>4773</v>
       </c>
       <c r="B7" s="2">
-        <v>46142.0625</v>
+        <v>46146.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5241</v>
+        <v>4701</v>
       </c>
       <c r="B8" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5021</v>
+        <v>4750</v>
       </c>
       <c r="B9" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4859</v>
+        <v>4731</v>
       </c>
       <c r="B10" s="2">
-        <v>46142.09375</v>
+        <v>46146.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4872</v>
+        <v>4692</v>
       </c>
       <c r="B11" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4867</v>
+        <v>4703</v>
       </c>
       <c r="B12" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4837</v>
+        <v>4713</v>
       </c>
       <c r="B13" s="2">
-        <v>46142.125</v>
+        <v>46146.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4872</v>
+        <v>4784</v>
       </c>
       <c r="B14" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4930</v>
+        <v>4736</v>
       </c>
       <c r="B15" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4865</v>
+        <v>4802</v>
       </c>
       <c r="B16" s="2">
-        <v>46142.15625</v>
+        <v>46146.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4874</v>
+        <v>4888</v>
       </c>
       <c r="B17" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5437</v>
+        <v>4985</v>
       </c>
       <c r="B18" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5576</v>
+        <v>5025</v>
       </c>
       <c r="B19" s="2">
-        <v>46142.1875</v>
+        <v>46146.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5596</v>
+        <v>5049</v>
       </c>
       <c r="B20" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5609</v>
+        <v>5118</v>
       </c>
       <c r="B21" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5724</v>
+        <v>5225</v>
       </c>
       <c r="B22" s="2">
-        <v>46142.21875</v>
+        <v>46146.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5907</v>
+        <v>5310</v>
       </c>
       <c r="B23" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>6050</v>
+        <v>5552</v>
       </c>
       <c r="B24" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6319</v>
+        <v>5709</v>
       </c>
       <c r="B25" s="2">
-        <v>46142.25</v>
+        <v>46146.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6425</v>
+        <v>5847</v>
       </c>
       <c r="B26" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6508</v>
+        <v>5918</v>
       </c>
       <c r="B27" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6573</v>
+        <v>5928</v>
       </c>
       <c r="B28" s="2">
-        <v>46142.28125</v>
+        <v>46146.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6712</v>
+        <v>5916</v>
       </c>
       <c r="B29" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6887</v>
+        <v>5925</v>
       </c>
       <c r="B30" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6879</v>
+        <v>5835</v>
       </c>
       <c r="B31" s="2">
-        <v>46142.3125</v>
+        <v>46146.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6788</v>
+        <v>5756</v>
       </c>
       <c r="B32" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6738</v>
+        <v>5622</v>
       </c>
       <c r="B33" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6813</v>
+        <v>5455</v>
       </c>
       <c r="B34" s="2">
-        <v>46142.34375</v>
+        <v>46146.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6723</v>
+        <v>5314</v>
       </c>
       <c r="B35" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6650</v>
+        <v>5132</v>
       </c>
       <c r="B36" s="2">
-        <v>46142.36458333334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>6630</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46142.375</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>6540</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46142.38541666666</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>6409</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46142.39583333334</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>6429</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46142.40625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>6245</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46142.41666666666</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>6260</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46142.42708333334</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>6170</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46142.4375</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>6093</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46142.44791666666</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>6089</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46142.45833333334</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>6135</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46142.46875</v>
+        <v>46146.35416666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,282 +394,242 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4898</v>
+        <v>5206</v>
       </c>
       <c r="B2" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4875</v>
+        <v>5131</v>
       </c>
       <c r="B3" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4816</v>
+        <v>5072</v>
       </c>
       <c r="B4" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4740</v>
+        <v>5054</v>
       </c>
       <c r="B5" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4743</v>
+        <v>5021</v>
       </c>
       <c r="B6" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4773</v>
+        <v>5175</v>
       </c>
       <c r="B7" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4701</v>
+        <v>5168</v>
       </c>
       <c r="B8" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4750</v>
+        <v>5102</v>
       </c>
       <c r="B9" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4731</v>
+        <v>5077</v>
       </c>
       <c r="B10" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4692</v>
+        <v>5042</v>
       </c>
       <c r="B11" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4703</v>
+        <v>5077</v>
       </c>
       <c r="B12" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4713</v>
+        <v>5028</v>
       </c>
       <c r="B13" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4784</v>
+        <v>5180</v>
       </c>
       <c r="B14" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4736</v>
+        <v>5173</v>
       </c>
       <c r="B15" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4802</v>
+        <v>5202</v>
       </c>
       <c r="B16" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4888</v>
+        <v>5207</v>
       </c>
       <c r="B17" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4985</v>
+        <v>5140</v>
       </c>
       <c r="B18" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5025</v>
+        <v>5188</v>
       </c>
       <c r="B19" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5049</v>
+        <v>5205</v>
       </c>
       <c r="B20" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5118</v>
+        <v>5246</v>
       </c>
       <c r="B21" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5225</v>
+        <v>5369</v>
       </c>
       <c r="B22" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5310</v>
+        <v>5430</v>
       </c>
       <c r="B23" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5552</v>
+        <v>5597</v>
       </c>
       <c r="B24" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5709</v>
+        <v>5673</v>
       </c>
       <c r="B25" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5847</v>
+        <v>5837</v>
       </c>
       <c r="B26" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5918</v>
+        <v>5843</v>
       </c>
       <c r="B27" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5928</v>
+        <v>5832</v>
       </c>
       <c r="B28" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5916</v>
+        <v>5768</v>
       </c>
       <c r="B29" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5925</v>
+        <v>5790</v>
       </c>
       <c r="B30" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5835</v>
+        <v>5694</v>
       </c>
       <c r="B31" s="2">
-        <v>46146.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>5756</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46146.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>5622</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46146.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>5455</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46146.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>5314</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46146.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>5132</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.30208333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,242 +394,266 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5206</v>
+        <v>5294</v>
       </c>
       <c r="B2" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5131</v>
+        <v>5229</v>
       </c>
       <c r="B3" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5072</v>
+        <v>5132</v>
       </c>
       <c r="B4" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5054</v>
+        <v>5183</v>
       </c>
       <c r="B5" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5021</v>
+        <v>5245</v>
       </c>
       <c r="B6" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5175</v>
+        <v>5252</v>
       </c>
       <c r="B7" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5168</v>
+        <v>5211</v>
       </c>
       <c r="B8" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5102</v>
+        <v>5185</v>
       </c>
       <c r="B9" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5077</v>
+        <v>5201</v>
       </c>
       <c r="B10" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5042</v>
+        <v>5217</v>
       </c>
       <c r="B11" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5077</v>
+        <v>5162</v>
       </c>
       <c r="B12" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5028</v>
+        <v>5205</v>
       </c>
       <c r="B13" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5180</v>
+        <v>5164</v>
       </c>
       <c r="B14" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5173</v>
+        <v>5211</v>
       </c>
       <c r="B15" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5202</v>
+        <v>5174</v>
       </c>
       <c r="B16" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5207</v>
+        <v>5199</v>
       </c>
       <c r="B17" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5140</v>
+        <v>5191</v>
       </c>
       <c r="B18" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5188</v>
+        <v>5260</v>
       </c>
       <c r="B19" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5205</v>
+        <v>5320</v>
       </c>
       <c r="B20" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5246</v>
+        <v>5321</v>
       </c>
       <c r="B21" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5369</v>
+        <v>5393</v>
       </c>
       <c r="B22" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5430</v>
+        <v>5473</v>
       </c>
       <c r="B23" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5597</v>
+        <v>5548</v>
       </c>
       <c r="B24" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5673</v>
+        <v>5646</v>
       </c>
       <c r="B25" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5837</v>
+        <v>5899</v>
       </c>
       <c r="B26" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5843</v>
+        <v>5924</v>
       </c>
       <c r="B27" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5832</v>
+        <v>6030</v>
       </c>
       <c r="B28" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5768</v>
+        <v>6070</v>
       </c>
       <c r="B29" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5790</v>
+        <v>6104</v>
       </c>
       <c r="B30" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5694</v>
+        <v>6004</v>
       </c>
       <c r="B31" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>6026</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46150.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>5885</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46150.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>5813</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46150.33333333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,266 +394,338 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5294</v>
+        <v>4655</v>
       </c>
       <c r="B2" s="2">
-        <v>46150</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5229</v>
+        <v>4595</v>
       </c>
       <c r="B3" s="2">
-        <v>46150.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5132</v>
+        <v>4578</v>
       </c>
       <c r="B4" s="2">
-        <v>46150.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5183</v>
+        <v>4573</v>
       </c>
       <c r="B5" s="2">
-        <v>46150.03125</v>
+        <v>46153.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5245</v>
+        <v>4640</v>
       </c>
       <c r="B6" s="2">
-        <v>46150.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5252</v>
+        <v>4637</v>
       </c>
       <c r="B7" s="2">
-        <v>46150.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5211</v>
+        <v>4649</v>
       </c>
       <c r="B8" s="2">
-        <v>46150.0625</v>
+        <v>46153.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5185</v>
+        <v>4674</v>
       </c>
       <c r="B9" s="2">
-        <v>46150.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5201</v>
+        <v>4652</v>
       </c>
       <c r="B10" s="2">
-        <v>46150.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5217</v>
+        <v>4695</v>
       </c>
       <c r="B11" s="2">
-        <v>46150.09375</v>
+        <v>46153.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5162</v>
+        <v>4691</v>
       </c>
       <c r="B12" s="2">
-        <v>46150.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5205</v>
+        <v>4694</v>
       </c>
       <c r="B13" s="2">
-        <v>46150.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5164</v>
+        <v>4693</v>
       </c>
       <c r="B14" s="2">
-        <v>46150.125</v>
+        <v>46153.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5211</v>
+        <v>4749</v>
       </c>
       <c r="B15" s="2">
-        <v>46150.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5174</v>
+        <v>4740</v>
       </c>
       <c r="B16" s="2">
-        <v>46150.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5199</v>
+        <v>4766</v>
       </c>
       <c r="B17" s="2">
-        <v>46150.15625</v>
+        <v>46153.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5191</v>
+        <v>4781</v>
       </c>
       <c r="B18" s="2">
-        <v>46150.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5260</v>
+        <v>4808</v>
       </c>
       <c r="B19" s="2">
-        <v>46150.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5320</v>
+        <v>4843</v>
       </c>
       <c r="B20" s="2">
-        <v>46150.1875</v>
+        <v>46153.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5321</v>
+        <v>4881</v>
       </c>
       <c r="B21" s="2">
-        <v>46150.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5393</v>
+        <v>4967</v>
       </c>
       <c r="B22" s="2">
-        <v>46150.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5473</v>
+        <v>5128</v>
       </c>
       <c r="B23" s="2">
-        <v>46150.21875</v>
+        <v>46153.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5548</v>
+        <v>5250</v>
       </c>
       <c r="B24" s="2">
-        <v>46150.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5646</v>
+        <v>5373</v>
       </c>
       <c r="B25" s="2">
-        <v>46150.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5899</v>
+        <v>5566</v>
       </c>
       <c r="B26" s="2">
-        <v>46150.25</v>
+        <v>46153.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5924</v>
+        <v>5608</v>
       </c>
       <c r="B27" s="2">
-        <v>46150.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6030</v>
+        <v>5672</v>
       </c>
       <c r="B28" s="2">
-        <v>46150.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6070</v>
+        <v>5600</v>
       </c>
       <c r="B29" s="2">
-        <v>46150.28125</v>
+        <v>46153.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6104</v>
+        <v>5595</v>
       </c>
       <c r="B30" s="2">
-        <v>46150.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6004</v>
+        <v>5628</v>
       </c>
       <c r="B31" s="2">
-        <v>46150.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6026</v>
+        <v>5459</v>
       </c>
       <c r="B32" s="2">
-        <v>46150.3125</v>
+        <v>46153.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5885</v>
+        <v>5368</v>
       </c>
       <c r="B33" s="2">
-        <v>46150.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5813</v>
+        <v>5215</v>
       </c>
       <c r="B34" s="2">
-        <v>46150.33333333334</v>
+        <v>46153.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>5207</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46153.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>5031</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46153.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>4939</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46153.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>4780</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46153.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>4599</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46153.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>4532</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46153.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>4540</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46153.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>4395</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46153.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>4285</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46153.42708333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,338 +394,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4655</v>
+        <v>5066</v>
       </c>
       <c r="B2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4595</v>
+        <v>5081</v>
       </c>
       <c r="B3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4578</v>
+        <v>5057</v>
       </c>
       <c r="B4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4573</v>
+        <v>4974</v>
       </c>
       <c r="B5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4640</v>
+        <v>5058</v>
       </c>
       <c r="B6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4637</v>
+        <v>5066</v>
       </c>
       <c r="B7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4649</v>
+        <v>5056</v>
       </c>
       <c r="B8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4674</v>
+        <v>4993</v>
       </c>
       <c r="B9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4652</v>
+        <v>4945</v>
       </c>
       <c r="B10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4695</v>
+        <v>4939</v>
       </c>
       <c r="B11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4691</v>
+        <v>4971</v>
       </c>
       <c r="B12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4694</v>
+        <v>5002</v>
       </c>
       <c r="B13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4693</v>
+        <v>4910</v>
       </c>
       <c r="B14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4749</v>
+        <v>4974</v>
       </c>
       <c r="B15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4740</v>
+        <v>5016</v>
       </c>
       <c r="B16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4766</v>
+        <v>4952</v>
       </c>
       <c r="B17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4781</v>
+        <v>5000</v>
       </c>
       <c r="B18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4808</v>
+        <v>5089</v>
       </c>
       <c r="B19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4843</v>
+        <v>5111</v>
       </c>
       <c r="B20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4881</v>
+        <v>5119</v>
       </c>
       <c r="B21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4967</v>
+        <v>5254</v>
       </c>
       <c r="B22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5128</v>
+        <v>5272</v>
       </c>
       <c r="B23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5250</v>
+        <v>5331</v>
       </c>
       <c r="B24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5373</v>
+        <v>5473</v>
       </c>
       <c r="B25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5566</v>
+        <v>5788</v>
       </c>
       <c r="B26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5608</v>
+        <v>5894</v>
       </c>
       <c r="B27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5672</v>
+        <v>5962</v>
       </c>
       <c r="B28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5600</v>
+        <v>6035</v>
       </c>
       <c r="B29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5595</v>
+        <v>6048</v>
       </c>
       <c r="B30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5628</v>
+        <v>6073</v>
       </c>
       <c r="B31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5459</v>
+        <v>6071</v>
       </c>
       <c r="B32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5368</v>
+        <v>6035</v>
       </c>
       <c r="B33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5215</v>
+        <v>5981</v>
       </c>
       <c r="B34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5207</v>
+        <v>5939</v>
       </c>
       <c r="B35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5031</v>
+        <v>5926</v>
       </c>
       <c r="B36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>4939</v>
+        <v>5860</v>
       </c>
       <c r="B37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>4780</v>
+        <v>5743</v>
       </c>
       <c r="B38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>4599</v>
+        <v>5773</v>
       </c>
       <c r="B39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>4532</v>
+        <v>5702</v>
       </c>
       <c r="B40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>4540</v>
+        <v>5602</v>
       </c>
       <c r="B41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>4395</v>
+        <v>5592</v>
       </c>
       <c r="B42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>4285</v>
+        <v>5569</v>
       </c>
       <c r="B43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>5647</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46155.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>5501</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46155.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>5486</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46155.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>5445</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46155.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>5509</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46155.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>5405</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46155.48958333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>5506</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46155.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>5674</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46155.51041666666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>5687</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46155.52083333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>5641</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46155.53125</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,418 +394,346 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5066</v>
+        <v>5280</v>
       </c>
       <c r="B2" s="2">
-        <v>46155</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5081</v>
+        <v>5219</v>
       </c>
       <c r="B3" s="2">
-        <v>46155.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5057</v>
+        <v>5184</v>
       </c>
       <c r="B4" s="2">
-        <v>46155.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4974</v>
+        <v>5107</v>
       </c>
       <c r="B5" s="2">
-        <v>46155.03125</v>
+        <v>46157.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5058</v>
+        <v>5178</v>
       </c>
       <c r="B6" s="2">
-        <v>46155.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5066</v>
+        <v>5200</v>
       </c>
       <c r="B7" s="2">
-        <v>46155.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5056</v>
+        <v>5134</v>
       </c>
       <c r="B8" s="2">
-        <v>46155.0625</v>
+        <v>46157.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4993</v>
+        <v>5159</v>
       </c>
       <c r="B9" s="2">
-        <v>46155.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4945</v>
+        <v>5104</v>
       </c>
       <c r="B10" s="2">
-        <v>46155.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4939</v>
+        <v>5098</v>
       </c>
       <c r="B11" s="2">
-        <v>46155.09375</v>
+        <v>46157.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4971</v>
+        <v>5093</v>
       </c>
       <c r="B12" s="2">
-        <v>46155.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5002</v>
+        <v>5118</v>
       </c>
       <c r="B13" s="2">
-        <v>46155.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4910</v>
+        <v>5059</v>
       </c>
       <c r="B14" s="2">
-        <v>46155.125</v>
+        <v>46157.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4974</v>
+        <v>5086</v>
       </c>
       <c r="B15" s="2">
-        <v>46155.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5016</v>
+        <v>5088</v>
       </c>
       <c r="B16" s="2">
-        <v>46155.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4952</v>
+        <v>5099</v>
       </c>
       <c r="B17" s="2">
-        <v>46155.15625</v>
+        <v>46157.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5000</v>
+        <v>5109</v>
       </c>
       <c r="B18" s="2">
-        <v>46155.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5089</v>
+        <v>5160</v>
       </c>
       <c r="B19" s="2">
-        <v>46155.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5111</v>
+        <v>5092</v>
       </c>
       <c r="B20" s="2">
-        <v>46155.1875</v>
+        <v>46157.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5119</v>
+        <v>5140</v>
       </c>
       <c r="B21" s="2">
-        <v>46155.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5254</v>
+        <v>5195</v>
       </c>
       <c r="B22" s="2">
-        <v>46155.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5272</v>
+        <v>5261</v>
       </c>
       <c r="B23" s="2">
-        <v>46155.21875</v>
+        <v>46157.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5331</v>
+        <v>5335</v>
       </c>
       <c r="B24" s="2">
-        <v>46155.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5473</v>
+        <v>5431</v>
       </c>
       <c r="B25" s="2">
-        <v>46155.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5788</v>
+        <v>5533</v>
       </c>
       <c r="B26" s="2">
-        <v>46155.25</v>
+        <v>46157.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5894</v>
+        <v>5638</v>
       </c>
       <c r="B27" s="2">
-        <v>46155.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5962</v>
+        <v>5655</v>
       </c>
       <c r="B28" s="2">
-        <v>46155.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6035</v>
+        <v>5639</v>
       </c>
       <c r="B29" s="2">
-        <v>46155.28125</v>
+        <v>46157.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6048</v>
+        <v>5563</v>
       </c>
       <c r="B30" s="2">
-        <v>46155.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6073</v>
+        <v>5570</v>
       </c>
       <c r="B31" s="2">
-        <v>46155.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6071</v>
+        <v>5477</v>
       </c>
       <c r="B32" s="2">
-        <v>46155.3125</v>
+        <v>46157.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6035</v>
+        <v>5352</v>
       </c>
       <c r="B33" s="2">
-        <v>46155.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5981</v>
+        <v>5164</v>
       </c>
       <c r="B34" s="2">
-        <v>46155.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5939</v>
+        <v>5072</v>
       </c>
       <c r="B35" s="2">
-        <v>46155.34375</v>
+        <v>46157.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5926</v>
+        <v>4963</v>
       </c>
       <c r="B36" s="2">
-        <v>46155.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5860</v>
+        <v>4827</v>
       </c>
       <c r="B37" s="2">
-        <v>46155.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>5743</v>
+        <v>4580</v>
       </c>
       <c r="B38" s="2">
-        <v>46155.375</v>
+        <v>46157.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>5773</v>
+        <v>4482</v>
       </c>
       <c r="B39" s="2">
-        <v>46155.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>5702</v>
+        <v>4348</v>
       </c>
       <c r="B40" s="2">
-        <v>46155.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>5602</v>
+        <v>4249</v>
       </c>
       <c r="B41" s="2">
-        <v>46155.40625</v>
+        <v>46157.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>5592</v>
+        <v>4159</v>
       </c>
       <c r="B42" s="2">
-        <v>46155.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>5569</v>
+        <v>4037</v>
       </c>
       <c r="B43" s="2">
-        <v>46155.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>5647</v>
+        <v>3991</v>
       </c>
       <c r="B44" s="2">
-        <v>46155.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>5501</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46155.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>5486</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46155.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>5445</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46155.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>5509</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46155.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>5405</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46155.48958333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>5506</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46155.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>5674</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46155.51041666666</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>5687</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46155.52083333334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>5641</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46155.53125</v>
+        <v>46157.4375</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,346 +394,418 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5280</v>
+        <v>5099</v>
       </c>
       <c r="B2" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5219</v>
+        <v>5084</v>
       </c>
       <c r="B3" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5184</v>
+        <v>5047</v>
       </c>
       <c r="B4" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5107</v>
+        <v>5004</v>
       </c>
       <c r="B5" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5178</v>
+        <v>5044</v>
       </c>
       <c r="B6" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5200</v>
+        <v>5025</v>
       </c>
       <c r="B7" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5134</v>
+        <v>5021</v>
       </c>
       <c r="B8" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5159</v>
+        <v>4990</v>
       </c>
       <c r="B9" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5104</v>
+        <v>4968</v>
       </c>
       <c r="B10" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5098</v>
+        <v>4997</v>
       </c>
       <c r="B11" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5093</v>
+        <v>4986</v>
       </c>
       <c r="B12" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5118</v>
+        <v>5012</v>
       </c>
       <c r="B13" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5059</v>
+        <v>4975</v>
       </c>
       <c r="B14" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5086</v>
+        <v>5016</v>
       </c>
       <c r="B15" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5088</v>
+        <v>5042</v>
       </c>
       <c r="B16" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5099</v>
+        <v>5083</v>
       </c>
       <c r="B17" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5109</v>
+        <v>5138</v>
       </c>
       <c r="B18" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5160</v>
+        <v>5193</v>
       </c>
       <c r="B19" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5092</v>
+        <v>5129</v>
       </c>
       <c r="B20" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5140</v>
+        <v>5183</v>
       </c>
       <c r="B21" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5195</v>
+        <v>5194</v>
       </c>
       <c r="B22" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5261</v>
+        <v>5255</v>
       </c>
       <c r="B23" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5335</v>
+        <v>5341</v>
       </c>
       <c r="B24" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5431</v>
+        <v>5474</v>
       </c>
       <c r="B25" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5533</v>
+        <v>5677</v>
       </c>
       <c r="B26" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5638</v>
+        <v>5757</v>
       </c>
       <c r="B27" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5655</v>
+        <v>5829</v>
       </c>
       <c r="B28" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5639</v>
+        <v>5814</v>
       </c>
       <c r="B29" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5563</v>
+        <v>5842</v>
       </c>
       <c r="B30" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5570</v>
+        <v>5833</v>
       </c>
       <c r="B31" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5477</v>
+        <v>5828</v>
       </c>
       <c r="B32" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5352</v>
+        <v>5815</v>
       </c>
       <c r="B33" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5164</v>
+        <v>5763</v>
       </c>
       <c r="B34" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5072</v>
+        <v>5782</v>
       </c>
       <c r="B35" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>4963</v>
+        <v>5687</v>
       </c>
       <c r="B36" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>4827</v>
+        <v>5657</v>
       </c>
       <c r="B37" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>4580</v>
+        <v>5541</v>
       </c>
       <c r="B38" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>4482</v>
+        <v>5581</v>
       </c>
       <c r="B39" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>4348</v>
+        <v>5549</v>
       </c>
       <c r="B40" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>4249</v>
+        <v>5496</v>
       </c>
       <c r="B41" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>4159</v>
+        <v>5323</v>
       </c>
       <c r="B42" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>4037</v>
+        <v>5255</v>
       </c>
       <c r="B43" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>3991</v>
+        <v>5203</v>
       </c>
       <c r="B44" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>5220</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46163.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>5307</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46163.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>5294</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46163.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>5321</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46163.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>5355</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46163.48958333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>5542</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46163.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>5604</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46163.51041666666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>5544</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46163.52083333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>5580</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46163.53125</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,418 +394,402 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5099</v>
+        <v>5139</v>
       </c>
       <c r="B2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5084</v>
+        <v>5071</v>
       </c>
       <c r="B3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5047</v>
+        <v>5012</v>
       </c>
       <c r="B4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5004</v>
+        <v>4995</v>
       </c>
       <c r="B5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5044</v>
+        <v>5061</v>
       </c>
       <c r="B6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5025</v>
+        <v>5053</v>
       </c>
       <c r="B7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5021</v>
+        <v>5034</v>
       </c>
       <c r="B8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4990</v>
+        <v>5003</v>
       </c>
       <c r="B9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4968</v>
+        <v>4984</v>
       </c>
       <c r="B10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4997</v>
+        <v>5009</v>
       </c>
       <c r="B11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4986</v>
+        <v>5007</v>
       </c>
       <c r="B12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5012</v>
+        <v>5030</v>
       </c>
       <c r="B13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4975</v>
+        <v>5051</v>
       </c>
       <c r="B14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5016</v>
+        <v>5022</v>
       </c>
       <c r="B15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5042</v>
+        <v>4987</v>
       </c>
       <c r="B16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5083</v>
+        <v>5001</v>
       </c>
       <c r="B17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5138</v>
+        <v>5033</v>
       </c>
       <c r="B18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5193</v>
+        <v>5013</v>
       </c>
       <c r="B19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5129</v>
+        <v>5040</v>
       </c>
       <c r="B20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5183</v>
+        <v>5049</v>
       </c>
       <c r="B21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5194</v>
+        <v>5190</v>
       </c>
       <c r="B22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5255</v>
+        <v>5270</v>
       </c>
       <c r="B23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5341</v>
+        <v>5388</v>
       </c>
       <c r="B24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5474</v>
+        <v>5477</v>
       </c>
       <c r="B25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5677</v>
+        <v>5726</v>
       </c>
       <c r="B26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5757</v>
+        <v>5863</v>
       </c>
       <c r="B27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5829</v>
+        <v>5943</v>
       </c>
       <c r="B28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5814</v>
+        <v>6058</v>
       </c>
       <c r="B29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5842</v>
+        <v>6126</v>
       </c>
       <c r="B30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5833</v>
+        <v>6224</v>
       </c>
       <c r="B31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5828</v>
+        <v>6163</v>
       </c>
       <c r="B32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5815</v>
+        <v>6111</v>
       </c>
       <c r="B33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5763</v>
+        <v>6052</v>
       </c>
       <c r="B34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5782</v>
+        <v>5979</v>
       </c>
       <c r="B35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5687</v>
+        <v>5929</v>
       </c>
       <c r="B36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5657</v>
+        <v>5862</v>
       </c>
       <c r="B37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>5541</v>
+        <v>5737</v>
       </c>
       <c r="B38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>5581</v>
+        <v>5621</v>
       </c>
       <c r="B39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>5549</v>
+        <v>5503</v>
       </c>
       <c r="B40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>5496</v>
+        <v>5342</v>
       </c>
       <c r="B41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>5323</v>
+        <v>5485</v>
       </c>
       <c r="B42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>5255</v>
+        <v>5159</v>
       </c>
       <c r="B43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>5203</v>
+        <v>5117</v>
       </c>
       <c r="B44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>5220</v>
+        <v>5105</v>
       </c>
       <c r="B45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>5307</v>
+        <v>5152</v>
       </c>
       <c r="B46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>5294</v>
+        <v>5090</v>
       </c>
       <c r="B47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>5321</v>
+        <v>5130</v>
       </c>
       <c r="B48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>5355</v>
+        <v>5116</v>
       </c>
       <c r="B49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>5542</v>
+        <v>5060</v>
       </c>
       <c r="B50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>5604</v>
+        <v>5118</v>
       </c>
       <c r="B51" s="2">
-        <v>46163.51041666666</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>5544</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46163.52083333334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>5580</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46163.53125</v>
+        <v>46164.51041666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,402 +394,346 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5139</v>
+        <v>4466</v>
       </c>
       <c r="B2" s="2">
-        <v>46164</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5071</v>
+        <v>4414</v>
       </c>
       <c r="B3" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5012</v>
+        <v>4369</v>
       </c>
       <c r="B4" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4995</v>
+        <v>4350</v>
       </c>
       <c r="B5" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5061</v>
+        <v>4401</v>
       </c>
       <c r="B6" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5053</v>
+        <v>4379</v>
       </c>
       <c r="B7" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5034</v>
+        <v>4364</v>
       </c>
       <c r="B8" s="2">
-        <v>46164.0625</v>
+        <v>46167.07291666666</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5003</v>
+        <v>4367</v>
       </c>
       <c r="B9" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.08333333334</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4984</v>
+        <v>4391</v>
       </c>
       <c r="B10" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.09375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5009</v>
+        <v>4397</v>
       </c>
       <c r="B11" s="2">
-        <v>46164.09375</v>
+        <v>46167.10416666666</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5007</v>
+        <v>4393</v>
       </c>
       <c r="B12" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.11458333334</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5030</v>
+        <v>4426</v>
       </c>
       <c r="B13" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5051</v>
+        <v>4536</v>
       </c>
       <c r="B14" s="2">
-        <v>46164.125</v>
+        <v>46167.13541666666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5022</v>
+        <v>4568</v>
       </c>
       <c r="B15" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.14583333334</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4987</v>
+        <v>4584</v>
       </c>
       <c r="B16" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.15625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5001</v>
+        <v>4611</v>
       </c>
       <c r="B17" s="2">
-        <v>46164.15625</v>
+        <v>46167.16666666666</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5033</v>
+        <v>4602</v>
       </c>
       <c r="B18" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.17708333334</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5013</v>
+        <v>4607</v>
       </c>
       <c r="B19" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.1875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5040</v>
+        <v>4660</v>
       </c>
       <c r="B20" s="2">
-        <v>46164.1875</v>
+        <v>46167.19791666666</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5049</v>
+        <v>4692</v>
       </c>
       <c r="B21" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.20833333334</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5190</v>
+        <v>4802</v>
       </c>
       <c r="B22" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.21875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5270</v>
+        <v>4913</v>
       </c>
       <c r="B23" s="2">
-        <v>46164.21875</v>
+        <v>46167.22916666666</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5388</v>
+        <v>5057</v>
       </c>
       <c r="B24" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.23958333334</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5477</v>
+        <v>5199</v>
       </c>
       <c r="B25" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5726</v>
+        <v>5283</v>
       </c>
       <c r="B26" s="2">
-        <v>46164.25</v>
+        <v>46167.26041666666</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5863</v>
+        <v>5293</v>
       </c>
       <c r="B27" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.27083333334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5943</v>
+        <v>5272</v>
       </c>
       <c r="B28" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.28125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6058</v>
+        <v>5294</v>
       </c>
       <c r="B29" s="2">
-        <v>46164.28125</v>
+        <v>46167.29166666666</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6126</v>
+        <v>5243</v>
       </c>
       <c r="B30" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.30208333334</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6224</v>
+        <v>5191</v>
       </c>
       <c r="B31" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.3125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6163</v>
+        <v>5052</v>
       </c>
       <c r="B32" s="2">
-        <v>46164.3125</v>
+        <v>46167.32291666666</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6111</v>
+        <v>4941</v>
       </c>
       <c r="B33" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.33333333334</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6052</v>
+        <v>4854</v>
       </c>
       <c r="B34" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.34375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5979</v>
+        <v>4726</v>
       </c>
       <c r="B35" s="2">
-        <v>46164.34375</v>
+        <v>46167.35416666666</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5929</v>
+        <v>4643</v>
       </c>
       <c r="B36" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.36458333334</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5862</v>
+        <v>4497</v>
       </c>
       <c r="B37" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>5737</v>
+        <v>4444</v>
       </c>
       <c r="B38" s="2">
-        <v>46164.375</v>
+        <v>46167.38541666666</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>5621</v>
+        <v>4329</v>
       </c>
       <c r="B39" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.39583333334</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>5503</v>
+        <v>4320</v>
       </c>
       <c r="B40" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.40625</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>5342</v>
+        <v>4232</v>
       </c>
       <c r="B41" s="2">
-        <v>46164.40625</v>
+        <v>46167.41666666666</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>5485</v>
+        <v>4174</v>
       </c>
       <c r="B42" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.42708333334</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>5159</v>
+        <v>4129</v>
       </c>
       <c r="B43" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.4375</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>5117</v>
+        <v>4106</v>
       </c>
       <c r="B44" s="2">
-        <v>46164.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>5105</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46164.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>5152</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46164.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>5090</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46164.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>5130</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46164.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>5116</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46164.48958333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>5060</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46164.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>5118</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.44791666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,346 +394,290 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4466</v>
+        <v>5068</v>
       </c>
       <c r="B2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4414</v>
+        <v>4985</v>
       </c>
       <c r="B3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4369</v>
+        <v>5002</v>
       </c>
       <c r="B4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4350</v>
+        <v>4986</v>
       </c>
       <c r="B5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4401</v>
+        <v>4973</v>
       </c>
       <c r="B6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4379</v>
+        <v>4937</v>
       </c>
       <c r="B7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4364</v>
+        <v>4941</v>
       </c>
       <c r="B8" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4367</v>
+        <v>4942</v>
       </c>
       <c r="B9" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4391</v>
+        <v>4995</v>
       </c>
       <c r="B10" s="2">
-        <v>46167.09375</v>
+        <v>46168.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4397</v>
+        <v>5037</v>
       </c>
       <c r="B11" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4393</v>
+        <v>5030</v>
       </c>
       <c r="B12" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4426</v>
+        <v>4983</v>
       </c>
       <c r="B13" s="2">
-        <v>46167.125</v>
+        <v>46168.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4536</v>
+        <v>5016</v>
       </c>
       <c r="B14" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4568</v>
+        <v>5025</v>
       </c>
       <c r="B15" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4584</v>
+        <v>5002</v>
       </c>
       <c r="B16" s="2">
-        <v>46167.15625</v>
+        <v>46168.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4611</v>
+        <v>4886</v>
       </c>
       <c r="B17" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4602</v>
+        <v>4892</v>
       </c>
       <c r="B18" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4607</v>
+        <v>4869</v>
       </c>
       <c r="B19" s="2">
-        <v>46167.1875</v>
+        <v>46168.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4660</v>
+        <v>4830</v>
       </c>
       <c r="B20" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4692</v>
+        <v>4865</v>
       </c>
       <c r="B21" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4802</v>
+        <v>4996</v>
       </c>
       <c r="B22" s="2">
-        <v>46167.21875</v>
+        <v>46168.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>4913</v>
+        <v>5116</v>
       </c>
       <c r="B23" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5057</v>
+        <v>5154</v>
       </c>
       <c r="B24" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5199</v>
+        <v>5208</v>
       </c>
       <c r="B25" s="2">
-        <v>46167.25</v>
+        <v>46168.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5283</v>
+        <v>5388</v>
       </c>
       <c r="B26" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5293</v>
+        <v>5498</v>
       </c>
       <c r="B27" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5272</v>
+        <v>5463</v>
       </c>
       <c r="B28" s="2">
-        <v>46167.28125</v>
+        <v>46168.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5294</v>
+        <v>5438</v>
       </c>
       <c r="B29" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5243</v>
+        <v>5382</v>
       </c>
       <c r="B30" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5191</v>
+        <v>5321</v>
       </c>
       <c r="B31" s="2">
-        <v>46167.3125</v>
+        <v>46168.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5052</v>
+        <v>5254</v>
       </c>
       <c r="B32" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>4941</v>
+        <v>5163</v>
       </c>
       <c r="B33" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>4854</v>
+        <v>4993</v>
       </c>
       <c r="B34" s="2">
-        <v>46167.34375</v>
+        <v>46168.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>4726</v>
+        <v>4857</v>
       </c>
       <c r="B35" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>4643</v>
+        <v>4734</v>
       </c>
       <c r="B36" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>4497</v>
+        <v>4586</v>
       </c>
       <c r="B37" s="2">
-        <v>46167.375</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>4444</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46167.38541666666</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>4329</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46167.39583333334</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>4320</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46167.40625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>4232</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46167.41666666666</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>4174</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46167.42708333334</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>4129</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46167.4375</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>4106</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.36458333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,290 +394,426 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5068</v>
+        <v>5392</v>
       </c>
       <c r="B2" s="2">
-        <v>46168</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4985</v>
+        <v>5346</v>
       </c>
       <c r="B3" s="2">
-        <v>46168.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5002</v>
+        <v>5260</v>
       </c>
       <c r="B4" s="2">
-        <v>46168.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4986</v>
+        <v>5202</v>
       </c>
       <c r="B5" s="2">
-        <v>46168.03125</v>
+        <v>46185.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4973</v>
+        <v>5203</v>
       </c>
       <c r="B6" s="2">
-        <v>46168.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4937</v>
+        <v>5220</v>
       </c>
       <c r="B7" s="2">
-        <v>46168.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4941</v>
+        <v>5253</v>
       </c>
       <c r="B8" s="2">
-        <v>46168.0625</v>
+        <v>46185.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4942</v>
+        <v>5196</v>
       </c>
       <c r="B9" s="2">
-        <v>46168.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4995</v>
+        <v>5221</v>
       </c>
       <c r="B10" s="2">
-        <v>46168.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5037</v>
+        <v>5193</v>
       </c>
       <c r="B11" s="2">
-        <v>46168.09375</v>
+        <v>46185.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5030</v>
+        <v>5178</v>
       </c>
       <c r="B12" s="2">
-        <v>46168.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4983</v>
+        <v>5238</v>
       </c>
       <c r="B13" s="2">
-        <v>46168.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5016</v>
+        <v>5256</v>
       </c>
       <c r="B14" s="2">
-        <v>46168.125</v>
+        <v>46185.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5025</v>
+        <v>5275</v>
       </c>
       <c r="B15" s="2">
-        <v>46168.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5002</v>
+        <v>5289</v>
       </c>
       <c r="B16" s="2">
-        <v>46168.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4886</v>
+        <v>5272</v>
       </c>
       <c r="B17" s="2">
-        <v>46168.15625</v>
+        <v>46185.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4892</v>
+        <v>5280</v>
       </c>
       <c r="B18" s="2">
-        <v>46168.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4869</v>
+        <v>5228</v>
       </c>
       <c r="B19" s="2">
-        <v>46168.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4830</v>
+        <v>5240</v>
       </c>
       <c r="B20" s="2">
-        <v>46168.1875</v>
+        <v>46185.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4865</v>
+        <v>5393</v>
       </c>
       <c r="B21" s="2">
-        <v>46168.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4996</v>
+        <v>5382</v>
       </c>
       <c r="B22" s="2">
-        <v>46168.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5116</v>
+        <v>5467</v>
       </c>
       <c r="B23" s="2">
-        <v>46168.21875</v>
+        <v>46185.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5154</v>
+        <v>5496</v>
       </c>
       <c r="B24" s="2">
-        <v>46168.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5208</v>
+        <v>5656</v>
       </c>
       <c r="B25" s="2">
-        <v>46168.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5388</v>
+        <v>5926</v>
       </c>
       <c r="B26" s="2">
-        <v>46168.25</v>
+        <v>46185.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5498</v>
+        <v>6056</v>
       </c>
       <c r="B27" s="2">
-        <v>46168.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5463</v>
+        <v>6167</v>
       </c>
       <c r="B28" s="2">
-        <v>46168.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5438</v>
+        <v>6207</v>
       </c>
       <c r="B29" s="2">
-        <v>46168.28125</v>
+        <v>46185.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5382</v>
+        <v>6252</v>
       </c>
       <c r="B30" s="2">
-        <v>46168.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5321</v>
+        <v>6358</v>
       </c>
       <c r="B31" s="2">
-        <v>46168.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5254</v>
+        <v>6398</v>
       </c>
       <c r="B32" s="2">
-        <v>46168.3125</v>
+        <v>46185.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5163</v>
+        <v>6425</v>
       </c>
       <c r="B33" s="2">
-        <v>46168.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>4993</v>
+        <v>6415</v>
       </c>
       <c r="B34" s="2">
-        <v>46168.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>4857</v>
+        <v>6491</v>
       </c>
       <c r="B35" s="2">
-        <v>46168.34375</v>
+        <v>46185.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>4734</v>
+        <v>6433</v>
       </c>
       <c r="B36" s="2">
-        <v>46168.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>4586</v>
+        <v>6339</v>
       </c>
       <c r="B37" s="2">
-        <v>46168.36458333334</v>
+        <v>46185.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>6327</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46185.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>6266</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46185.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>6181</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46185.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>6015</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46185.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>5842</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46185.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>5701</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46185.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>5696</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46185.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>5611</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46185.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>5548</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46185.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>5450</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46185.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>5439</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46185.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>5449</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46185.48958333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>5515</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46185.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>5559</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46185.51041666666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>5527</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46185.52083333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>5453</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46185.53125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>5386</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46185.54166666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_5A99472AB030921FD2FE31D2F8375B069417EA81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAA54E66-A07A-4E5B-ADB5-A84E034F510B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A9FBC63BB030921FD2FE31D2F8375B06E498F46C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6583B4D-AF94-44BC-8CF6-D528CA6A0F31}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -427,362 +427,418 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5509</v>
+        <v>5030</v>
       </c>
       <c r="B2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5396</v>
+        <v>4963</v>
       </c>
       <c r="B3" s="2">
-        <v>46213.010416666657</v>
+        <v>46216.010416666657</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5402</v>
+        <v>4969</v>
       </c>
       <c r="B4" s="2">
-        <v>46213.020833333343</v>
+        <v>46216.020833333343</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5325</v>
+        <v>4866</v>
       </c>
       <c r="B5" s="2">
-        <v>46213.03125</v>
+        <v>46216.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5426</v>
+        <v>4810</v>
       </c>
       <c r="B6" s="2">
-        <v>46213.041666666657</v>
+        <v>46216.041666666657</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5441</v>
+        <v>4765</v>
       </c>
       <c r="B7" s="2">
-        <v>46213.052083333343</v>
+        <v>46216.052083333343</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5421</v>
+        <v>4724</v>
       </c>
       <c r="B8" s="2">
-        <v>46213.0625</v>
+        <v>46216.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>5389</v>
+        <v>4837</v>
       </c>
       <c r="B9" s="2">
-        <v>46213.072916666657</v>
+        <v>46216.072916666657</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5242</v>
+        <v>4909</v>
       </c>
       <c r="B10" s="2">
-        <v>46213.083333333343</v>
+        <v>46216.083333333343</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5426</v>
+        <v>4814</v>
       </c>
       <c r="B11" s="2">
-        <v>46213.09375</v>
+        <v>46216.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5181</v>
+        <v>4812</v>
       </c>
       <c r="B12" s="2">
-        <v>46213.104166666657</v>
+        <v>46216.104166666657</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5373</v>
+        <v>4827</v>
       </c>
       <c r="B13" s="2">
-        <v>46213.114583333343</v>
+        <v>46216.114583333343</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5420</v>
+        <v>4845</v>
       </c>
       <c r="B14" s="2">
-        <v>46213.125</v>
+        <v>46216.125</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5394</v>
+        <v>4907</v>
       </c>
       <c r="B15" s="2">
-        <v>46213.135416666657</v>
+        <v>46216.135416666657</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5379</v>
+        <v>4839</v>
       </c>
       <c r="B16" s="2">
-        <v>46213.145833333343</v>
+        <v>46216.145833333343</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5231</v>
+        <v>4846</v>
       </c>
       <c r="B17" s="2">
-        <v>46213.15625</v>
+        <v>46216.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5300</v>
+        <v>4905</v>
       </c>
       <c r="B18" s="2">
-        <v>46213.166666666657</v>
+        <v>46216.166666666657</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5287</v>
+        <v>4934</v>
       </c>
       <c r="B19" s="2">
-        <v>46213.177083333343</v>
+        <v>46216.177083333343</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5202</v>
+        <v>4950</v>
       </c>
       <c r="B20" s="2">
-        <v>46213.1875</v>
+        <v>46216.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5225</v>
+        <v>4935</v>
       </c>
       <c r="B21" s="2">
-        <v>46213.197916666657</v>
+        <v>46216.197916666657</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5311</v>
+        <v>5055</v>
       </c>
       <c r="B22" s="2">
-        <v>46213.208333333343</v>
+        <v>46216.208333333343</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5394</v>
+        <v>5112</v>
       </c>
       <c r="B23" s="2">
-        <v>46213.21875</v>
+        <v>46216.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>5403</v>
+        <v>5176</v>
       </c>
       <c r="B24" s="2">
-        <v>46213.229166666657</v>
+        <v>46216.229166666657</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>5514</v>
+        <v>5305</v>
       </c>
       <c r="B25" s="2">
-        <v>46213.239583333343</v>
+        <v>46216.239583333343</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>5707</v>
+        <v>5507</v>
       </c>
       <c r="B26" s="2">
-        <v>46213.25</v>
+        <v>46216.25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5692</v>
+        <v>5642</v>
       </c>
       <c r="B27" s="2">
-        <v>46213.260416666657</v>
+        <v>46216.260416666657</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5711</v>
+        <v>5773</v>
       </c>
       <c r="B28" s="2">
-        <v>46213.270833333343</v>
+        <v>46216.270833333343</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5778</v>
+        <v>5865</v>
       </c>
       <c r="B29" s="2">
-        <v>46213.28125</v>
+        <v>46216.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5791</v>
+        <v>5879</v>
       </c>
       <c r="B30" s="2">
-        <v>46213.291666666657</v>
+        <v>46216.291666666657</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>5789</v>
+        <v>5871</v>
       </c>
       <c r="B31" s="2">
-        <v>46213.302083333343</v>
+        <v>46216.302083333343</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5752</v>
+        <v>5894</v>
       </c>
       <c r="B32" s="2">
-        <v>46213.3125</v>
+        <v>46216.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5657</v>
+        <v>5847</v>
       </c>
       <c r="B33" s="2">
-        <v>46213.322916666657</v>
+        <v>46216.322916666657</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5505</v>
+        <v>5727</v>
       </c>
       <c r="B34" s="2">
-        <v>46213.333333333343</v>
+        <v>46216.333333333343</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5400</v>
+        <v>5695</v>
       </c>
       <c r="B35" s="2">
-        <v>46213.34375</v>
+        <v>46216.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5297</v>
+        <v>5617</v>
       </c>
       <c r="B36" s="2">
-        <v>46213.354166666657</v>
+        <v>46216.354166666657</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>5240</v>
+        <v>5496</v>
       </c>
       <c r="B37" s="2">
-        <v>46213.364583333343</v>
+        <v>46216.364583333343</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5099</v>
+        <v>5407</v>
       </c>
       <c r="B38" s="2">
-        <v>46213.375</v>
+        <v>46216.375</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>4940</v>
+        <v>5323</v>
       </c>
       <c r="B39" s="2">
-        <v>46213.385416666657</v>
+        <v>46216.385416666657</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>4858</v>
+        <v>5057</v>
       </c>
       <c r="B40" s="2">
-        <v>46213.395833333343</v>
+        <v>46216.395833333343</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>4851</v>
+        <v>5093</v>
       </c>
       <c r="B41" s="2">
-        <v>46213.40625</v>
+        <v>46216.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>4875</v>
+        <v>5095</v>
       </c>
       <c r="B42" s="2">
-        <v>46213.416666666657</v>
+        <v>46216.416666666657</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>4818</v>
+        <v>5017</v>
       </c>
       <c r="B43" s="2">
-        <v>46213.427083333343</v>
+        <v>46216.427083333343</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>4758</v>
+        <v>4951</v>
       </c>
       <c r="B44" s="2">
-        <v>46213.4375</v>
+        <v>46216.4375</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>4654</v>
+        <v>4982</v>
       </c>
       <c r="B45" s="2">
-        <v>46213.447916666657</v>
+        <v>46216.447916666657</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>4632</v>
+        <v>5098</v>
       </c>
       <c r="B46" s="2">
-        <v>46213.458333333343</v>
+        <v>46216.458333333343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>5202</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46216.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>5121</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46216.479166666657</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>5240</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46216.489583333343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>5305</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46216.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>5425</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46216.510416666657</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>5448</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46216.520833333343</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>5472</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46216.53125</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A9FBC63BB030921FD2FE31D2F8375B06E498F46C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6583B4D-AF94-44BC-8CF6-D528CA6A0F31}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,420 +392,364 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>5030</v>
+        <v>5553</v>
       </c>
       <c r="B2" s="2">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
-        <v>4963</v>
+        <v>5454</v>
       </c>
       <c r="B3" s="2">
-        <v>46216.010416666657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.01041666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
-        <v>4969</v>
+        <v>5413</v>
       </c>
       <c r="B4" s="2">
-        <v>46216.020833333343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.02083333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
-        <v>4866</v>
+        <v>5387</v>
       </c>
       <c r="B5" s="2">
-        <v>46216.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
-        <v>4810</v>
+        <v>5368</v>
       </c>
       <c r="B6" s="2">
-        <v>46216.041666666657</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.04166666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>4765</v>
+        <v>5264</v>
       </c>
       <c r="B7" s="2">
-        <v>46216.052083333343</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.05208333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
-        <v>4724</v>
+        <v>5243</v>
       </c>
       <c r="B8" s="2">
-        <v>46216.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
-        <v>4837</v>
+        <v>5219</v>
       </c>
       <c r="B9" s="2">
-        <v>46216.072916666657</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.07291666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
-        <v>4909</v>
+        <v>5277</v>
       </c>
       <c r="B10" s="2">
-        <v>46216.083333333343</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.08333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
-        <v>4814</v>
+        <v>5366</v>
       </c>
       <c r="B11" s="2">
-        <v>46216.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>4812</v>
+        <v>5377</v>
       </c>
       <c r="B12" s="2">
-        <v>46216.104166666657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.10416666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
-        <v>4827</v>
+        <v>5348</v>
       </c>
       <c r="B13" s="2">
-        <v>46216.114583333343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.11458333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>4845</v>
+        <v>5391</v>
       </c>
       <c r="B14" s="2">
-        <v>46216.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
-        <v>4907</v>
+        <v>5356</v>
       </c>
       <c r="B15" s="2">
-        <v>46216.135416666657</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.13541666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
-        <v>4839</v>
+        <v>5391</v>
       </c>
       <c r="B16" s="2">
-        <v>46216.145833333343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.14583333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>4846</v>
+        <v>5395</v>
       </c>
       <c r="B17" s="2">
-        <v>46216.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
-        <v>4905</v>
+        <v>5287</v>
       </c>
       <c r="B18" s="2">
-        <v>46216.166666666657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.16666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
-        <v>4934</v>
+        <v>5244</v>
       </c>
       <c r="B19" s="2">
-        <v>46216.177083333343</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.17708333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
-        <v>4950</v>
+        <v>5263</v>
       </c>
       <c r="B20" s="2">
-        <v>46216.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
-        <v>4935</v>
+        <v>5278</v>
       </c>
       <c r="B21" s="2">
-        <v>46216.197916666657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.19791666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>5055</v>
+        <v>5401</v>
       </c>
       <c r="B22" s="2">
-        <v>46216.208333333343</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.20833333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
-        <v>5112</v>
+        <v>5509</v>
       </c>
       <c r="B23" s="2">
-        <v>46216.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
-        <v>5176</v>
+        <v>5559</v>
       </c>
       <c r="B24" s="2">
-        <v>46216.229166666657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.22916666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
-        <v>5305</v>
+        <v>5613</v>
       </c>
       <c r="B25" s="2">
-        <v>46216.239583333343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.23958333334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
-        <v>5507</v>
+        <v>5753</v>
       </c>
       <c r="B26" s="2">
-        <v>46216.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>5642</v>
+        <v>5925</v>
       </c>
       <c r="B27" s="2">
-        <v>46216.260416666657</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.26041666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
-        <v>5773</v>
+        <v>5932</v>
       </c>
       <c r="B28" s="2">
-        <v>46216.270833333343</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.27083333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
-        <v>5865</v>
+        <v>5982</v>
       </c>
       <c r="B29" s="2">
-        <v>46216.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
-        <v>5879</v>
+        <v>6055</v>
       </c>
       <c r="B30" s="2">
-        <v>46216.291666666657</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.29166666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
-        <v>5871</v>
+        <v>6004</v>
       </c>
       <c r="B31" s="2">
-        <v>46216.302083333343</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
-        <v>5894</v>
+        <v>5901</v>
       </c>
       <c r="B32" s="2">
-        <v>46216.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
-        <v>5847</v>
+        <v>5792</v>
       </c>
       <c r="B33" s="2">
-        <v>46216.322916666657</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
-        <v>5727</v>
+        <v>5731</v>
       </c>
       <c r="B34" s="2">
-        <v>46216.333333333343</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
-        <v>5695</v>
+        <v>5631</v>
       </c>
       <c r="B35" s="2">
-        <v>46216.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
-        <v>5617</v>
+        <v>5526</v>
       </c>
       <c r="B36" s="2">
-        <v>46216.354166666657</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
-        <v>5496</v>
+        <v>5504</v>
       </c>
       <c r="B37" s="2">
-        <v>46216.364583333343</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
-        <v>5407</v>
+        <v>5389</v>
       </c>
       <c r="B38" s="2">
-        <v>46216.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
-        <v>5323</v>
+        <v>5350</v>
       </c>
       <c r="B39" s="2">
-        <v>46216.385416666657</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
-        <v>5057</v>
+        <v>5307</v>
       </c>
       <c r="B40" s="2">
-        <v>46216.395833333343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
-        <v>5093</v>
+        <v>5365</v>
       </c>
       <c r="B41" s="2">
-        <v>46216.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
-        <v>5095</v>
+        <v>5159</v>
       </c>
       <c r="B42" s="2">
-        <v>46216.416666666657</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
-        <v>5017</v>
+        <v>5049</v>
       </c>
       <c r="B43" s="2">
-        <v>46216.427083333343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
-        <v>4951</v>
+        <v>5152</v>
       </c>
       <c r="B44" s="2">
-        <v>46216.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
-        <v>4982</v>
+        <v>5129</v>
       </c>
       <c r="B45" s="2">
-        <v>46216.447916666657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46218.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
-        <v>5098</v>
+        <v>5028</v>
       </c>
       <c r="B46" s="2">
-        <v>46216.458333333343</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>5202</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46216.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>5121</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46216.479166666657</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>5240</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46216.489583333343</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>5305</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46216.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>5425</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46216.510416666657</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>5448</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46216.520833333343</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>5472</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46216.53125</v>
+        <v>46218.45833333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C9FD2438B030921FD2FE31D2F8375B0684100C04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C0360EB-8CB7-4405-AC18-23CE18B7A033}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,364 +425,348 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>5553</v>
+        <v>5739</v>
       </c>
       <c r="B2" s="2">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>5454</v>
+        <v>5616</v>
       </c>
       <c r="B3" s="2">
-        <v>46218.01041666666</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>46219.010416666657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>5413</v>
+        <v>5570</v>
       </c>
       <c r="B4" s="2">
-        <v>46218.02083333334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>46219.020833333343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5387</v>
+        <v>5619</v>
       </c>
       <c r="B5" s="2">
-        <v>46218.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>46219.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5368</v>
+        <v>5545</v>
       </c>
       <c r="B6" s="2">
-        <v>46218.04166666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>46219.041666666657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5264</v>
+        <v>5450</v>
       </c>
       <c r="B7" s="2">
-        <v>46218.05208333334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>46219.052083333343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>5243</v>
+        <v>5418</v>
       </c>
       <c r="B8" s="2">
-        <v>46218.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>46219.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>5219</v>
+        <v>5402</v>
       </c>
       <c r="B9" s="2">
-        <v>46218.07291666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>46219.072916666657</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>5277</v>
+        <v>5418</v>
       </c>
       <c r="B10" s="2">
-        <v>46218.08333333334</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>46219.083333333343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>5366</v>
+        <v>5319</v>
       </c>
       <c r="B11" s="2">
-        <v>46218.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>46219.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>5377</v>
+        <v>5305</v>
       </c>
       <c r="B12" s="2">
-        <v>46218.10416666666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>46219.104166666657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>5348</v>
+        <v>5401</v>
       </c>
       <c r="B13" s="2">
-        <v>46218.11458333334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>46219.114583333343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>5391</v>
+        <v>5489</v>
       </c>
       <c r="B14" s="2">
-        <v>46218.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>46219.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>5356</v>
+        <v>5492</v>
       </c>
       <c r="B15" s="2">
-        <v>46218.13541666666</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>46219.135416666657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>5391</v>
+        <v>5521</v>
       </c>
       <c r="B16" s="2">
-        <v>46218.14583333334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>46219.145833333343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>5395</v>
+        <v>5500</v>
       </c>
       <c r="B17" s="2">
-        <v>46218.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>46219.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>5287</v>
+        <v>5591</v>
       </c>
       <c r="B18" s="2">
-        <v>46218.16666666666</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>46219.166666666657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>5244</v>
+        <v>5651</v>
       </c>
       <c r="B19" s="2">
-        <v>46218.17708333334</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>46219.177083333343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>5263</v>
+        <v>5565</v>
       </c>
       <c r="B20" s="2">
-        <v>46218.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>46219.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>5278</v>
+        <v>5597</v>
       </c>
       <c r="B21" s="2">
-        <v>46218.19791666666</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>46219.197916666657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>5401</v>
+        <v>5625</v>
       </c>
       <c r="B22" s="2">
-        <v>46218.20833333334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>46219.208333333343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>5509</v>
+        <v>5628</v>
       </c>
       <c r="B23" s="2">
-        <v>46218.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>46219.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>5559</v>
+        <v>5683</v>
       </c>
       <c r="B24" s="2">
-        <v>46218.22916666666</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>46219.229166666657</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>5613</v>
+        <v>5796</v>
       </c>
       <c r="B25" s="2">
-        <v>46218.23958333334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>46219.239583333343</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>5753</v>
+        <v>5984</v>
       </c>
       <c r="B26" s="2">
-        <v>46218.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>46219.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>5925</v>
+        <v>6086</v>
       </c>
       <c r="B27" s="2">
-        <v>46218.26041666666</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>46219.260416666657</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>5932</v>
+        <v>6124</v>
       </c>
       <c r="B28" s="2">
-        <v>46218.27083333334</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>46219.270833333343</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>5982</v>
+        <v>6202</v>
       </c>
       <c r="B29" s="2">
-        <v>46218.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>46219.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>6055</v>
+        <v>6256</v>
       </c>
       <c r="B30" s="2">
-        <v>46218.29166666666</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>46219.291666666657</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>6004</v>
+        <v>6223</v>
       </c>
       <c r="B31" s="2">
-        <v>46218.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>46219.302083333343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>5901</v>
+        <v>6347</v>
       </c>
       <c r="B32" s="2">
-        <v>46218.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>46219.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>5792</v>
+        <v>6197</v>
       </c>
       <c r="B33" s="2">
-        <v>46218.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>46219.322916666657</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>5731</v>
+        <v>6059</v>
       </c>
       <c r="B34" s="2">
-        <v>46218.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>46219.333333333343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>5631</v>
+        <v>6026</v>
       </c>
       <c r="B35" s="2">
-        <v>46218.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>46219.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>5526</v>
+        <v>5948</v>
       </c>
       <c r="B36" s="2">
-        <v>46218.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>46219.354166666657</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>5504</v>
+        <v>5826</v>
       </c>
       <c r="B37" s="2">
-        <v>46218.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>46219.364583333343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>5389</v>
+        <v>5741</v>
       </c>
       <c r="B38" s="2">
-        <v>46218.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>46219.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>5350</v>
+        <v>5626</v>
       </c>
       <c r="B39" s="2">
-        <v>46218.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>46219.385416666657</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>5307</v>
+        <v>5711</v>
       </c>
       <c r="B40" s="2">
-        <v>46218.39583333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>46219.395833333343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>5365</v>
+        <v>5652</v>
       </c>
       <c r="B41" s="2">
-        <v>46218.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>46219.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>5159</v>
+        <v>5490</v>
       </c>
       <c r="B42" s="2">
-        <v>46218.41666666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>46219.416666666657</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>5049</v>
+        <v>5430</v>
       </c>
       <c r="B43" s="2">
-        <v>46218.42708333334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>46219.427083333343</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>5152</v>
+        <v>0</v>
       </c>
       <c r="B44" s="2">
-        <v>46218.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>5129</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46218.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>5028</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46218.45833333334</v>
+        <v>46219.4375</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_C9FD2438B030921FD2FE31D2F8375B0684100C04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C0360EB-8CB7-4405-AC18-23CE18B7A033}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,348 +392,244 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2">
-        <v>5739</v>
+        <v>5398</v>
       </c>
       <c r="B2" s="2">
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
-        <v>5616</v>
+        <v>5274</v>
       </c>
       <c r="B3" s="2">
-        <v>46219.010416666657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.01041666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
-        <v>5570</v>
+        <v>5216</v>
       </c>
       <c r="B4" s="2">
-        <v>46219.020833333343</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.02083333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
-        <v>5619</v>
+        <v>5145</v>
       </c>
       <c r="B5" s="2">
-        <v>46219.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.04166666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
-        <v>5545</v>
+        <v>5108</v>
       </c>
       <c r="B6" s="2">
-        <v>46219.041666666657</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.05208333334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
-        <v>5450</v>
+        <v>5087</v>
       </c>
       <c r="B7" s="2">
-        <v>46219.052083333343</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.0625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
-        <v>5418</v>
+        <v>5078</v>
       </c>
       <c r="B8" s="2">
-        <v>46219.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.07291666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
-        <v>5402</v>
+        <v>5135</v>
       </c>
       <c r="B9" s="2">
-        <v>46219.072916666657</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.08333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
-        <v>5418</v>
+        <v>5149</v>
       </c>
       <c r="B10" s="2">
-        <v>46219.083333333343</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.09375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
-        <v>5319</v>
+        <v>5132</v>
       </c>
       <c r="B11" s="2">
-        <v>46219.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.10416666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
-        <v>5305</v>
+        <v>5087</v>
       </c>
       <c r="B12" s="2">
-        <v>46219.104166666657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.11458333334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
-        <v>5401</v>
+        <v>5156</v>
       </c>
       <c r="B13" s="2">
-        <v>46219.114583333343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
-        <v>5489</v>
+        <v>5209</v>
       </c>
       <c r="B14" s="2">
-        <v>46219.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.13541666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
-        <v>5492</v>
+        <v>5215</v>
       </c>
       <c r="B15" s="2">
-        <v>46219.135416666657</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.14583333334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
-        <v>5521</v>
+        <v>5179</v>
       </c>
       <c r="B16" s="2">
-        <v>46219.145833333343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.15625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
-        <v>5500</v>
+        <v>5216</v>
       </c>
       <c r="B17" s="2">
-        <v>46219.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.16666666666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
-        <v>5591</v>
+        <v>5055</v>
       </c>
       <c r="B18" s="2">
-        <v>46219.166666666657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.17708333334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
-        <v>5651</v>
+        <v>5087</v>
       </c>
       <c r="B19" s="2">
-        <v>46219.177083333343</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.1875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
-        <v>5565</v>
+        <v>5143</v>
       </c>
       <c r="B20" s="2">
-        <v>46219.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.19791666666</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
-        <v>5597</v>
+        <v>5228</v>
       </c>
       <c r="B21" s="2">
-        <v>46219.197916666657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.20833333334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
-        <v>5625</v>
+        <v>5360</v>
       </c>
       <c r="B22" s="2">
-        <v>46219.208333333343</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.21875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
-        <v>5628</v>
+        <v>5421</v>
       </c>
       <c r="B23" s="2">
-        <v>46219.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.22916666666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
-        <v>5683</v>
+        <v>5548</v>
       </c>
       <c r="B24" s="2">
-        <v>46219.229166666657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.23958333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
-        <v>5796</v>
+        <v>5681</v>
       </c>
       <c r="B25" s="2">
-        <v>46219.239583333343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
-        <v>5984</v>
+        <v>5829</v>
       </c>
       <c r="B26" s="2">
-        <v>46219.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.26041666666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
-        <v>6086</v>
+        <v>5869</v>
       </c>
       <c r="B27" s="2">
-        <v>46219.260416666657</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.27083333334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
-        <v>6124</v>
+        <v>5967</v>
       </c>
       <c r="B28" s="2">
-        <v>46219.270833333343</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.28125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
-        <v>6202</v>
+        <v>6016</v>
       </c>
       <c r="B29" s="2">
-        <v>46219.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.29166666666</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
-        <v>6256</v>
+        <v>5987</v>
       </c>
       <c r="B30" s="2">
-        <v>46219.291666666657</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46223.30208333334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
-        <v>6223</v>
+        <v>6040</v>
       </c>
       <c r="B31" s="2">
-        <v>46219.302083333343</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>6347</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46219.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>6197</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46219.322916666657</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>6059</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46219.333333333343</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>6026</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46219.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>5948</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46219.354166666657</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>5826</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46219.364583333343</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>5741</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46219.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>5626</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46219.385416666657</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>5711</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46219.395833333343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>5652</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46219.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>5490</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46219.416666666657</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>5430</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46219.427083333343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>0</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46219.4375</v>
+        <v>46223.3125</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -394,242 +394,242 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5398</v>
+        <v>5187</v>
       </c>
       <c r="B2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5274</v>
+        <v>5144</v>
       </c>
       <c r="B3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5216</v>
+        <v>5106</v>
       </c>
       <c r="B4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5145</v>
+        <v>5079</v>
       </c>
       <c r="B5" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5108</v>
+        <v>5007</v>
       </c>
       <c r="B6" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5087</v>
+        <v>4968</v>
       </c>
       <c r="B7" s="2">
-        <v>46223.0625</v>
+        <v>46226.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5078</v>
+        <v>4941</v>
       </c>
       <c r="B8" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5135</v>
+        <v>4926</v>
       </c>
       <c r="B9" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5149</v>
+        <v>4902</v>
       </c>
       <c r="B10" s="2">
-        <v>46223.09375</v>
+        <v>46226.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5132</v>
+        <v>4880</v>
       </c>
       <c r="B11" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5087</v>
+        <v>4870</v>
       </c>
       <c r="B12" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5156</v>
+        <v>4879</v>
       </c>
       <c r="B13" s="2">
-        <v>46223.125</v>
+        <v>46226.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5209</v>
+        <v>4984</v>
       </c>
       <c r="B14" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5215</v>
+        <v>5013</v>
       </c>
       <c r="B15" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5179</v>
+        <v>4981</v>
       </c>
       <c r="B16" s="2">
-        <v>46223.15625</v>
+        <v>46226.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5216</v>
+        <v>4979</v>
       </c>
       <c r="B17" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5055</v>
+        <v>4940</v>
       </c>
       <c r="B18" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5087</v>
+        <v>4970</v>
       </c>
       <c r="B19" s="2">
-        <v>46223.1875</v>
+        <v>46226.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5143</v>
+        <v>5031</v>
       </c>
       <c r="B20" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5228</v>
+        <v>5057</v>
       </c>
       <c r="B21" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5360</v>
+        <v>5117</v>
       </c>
       <c r="B22" s="2">
-        <v>46223.21875</v>
+        <v>46226.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5421</v>
+        <v>5186</v>
       </c>
       <c r="B23" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5548</v>
+        <v>5262</v>
       </c>
       <c r="B24" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5681</v>
+        <v>5335</v>
       </c>
       <c r="B25" s="2">
-        <v>46223.25</v>
+        <v>46226.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5829</v>
+        <v>5467</v>
       </c>
       <c r="B26" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5869</v>
+        <v>5555</v>
       </c>
       <c r="B27" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5967</v>
+        <v>5595</v>
       </c>
       <c r="B28" s="2">
-        <v>46223.28125</v>
+        <v>46226.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6016</v>
+        <v>5662</v>
       </c>
       <c r="B29" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5987</v>
+        <v>5644</v>
       </c>
       <c r="B30" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6040</v>
+        <v>5652</v>
       </c>
       <c r="B31" s="2">
-        <v>46223.3125</v>
+        <v>46226.30208333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -397,239 +397,247 @@
         <v>5187</v>
       </c>
       <c r="B2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5144</v>
+        <v>5148</v>
       </c>
       <c r="B3" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5106</v>
+        <v>5105</v>
       </c>
       <c r="B4" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5079</v>
+        <v>5044</v>
       </c>
       <c r="B5" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5007</v>
+        <v>5008</v>
       </c>
       <c r="B6" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4968</v>
+        <v>4999</v>
       </c>
       <c r="B7" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4941</v>
+        <v>4990</v>
       </c>
       <c r="B8" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4926</v>
+        <v>5032</v>
       </c>
       <c r="B9" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4902</v>
+        <v>5042</v>
       </c>
       <c r="B10" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4880</v>
+        <v>5006</v>
       </c>
       <c r="B11" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4870</v>
+        <v>4968</v>
       </c>
       <c r="B12" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4879</v>
+        <v>4973</v>
       </c>
       <c r="B13" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4984</v>
+        <v>5026</v>
       </c>
       <c r="B14" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5013</v>
+        <v>5018</v>
       </c>
       <c r="B15" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4981</v>
+        <v>5084</v>
       </c>
       <c r="B16" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4979</v>
+        <v>5090</v>
       </c>
       <c r="B17" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4940</v>
+        <v>4967</v>
       </c>
       <c r="B18" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4970</v>
+        <v>4977</v>
       </c>
       <c r="B19" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5031</v>
+        <v>4978</v>
       </c>
       <c r="B20" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5057</v>
+        <v>5025</v>
       </c>
       <c r="B21" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5117</v>
+        <v>5129</v>
       </c>
       <c r="B22" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5186</v>
+        <v>5202</v>
       </c>
       <c r="B23" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5262</v>
+        <v>5313</v>
       </c>
       <c r="B24" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5335</v>
+        <v>5327</v>
       </c>
       <c r="B25" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5467</v>
+        <v>5476</v>
       </c>
       <c r="B26" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5555</v>
+        <v>5536</v>
       </c>
       <c r="B27" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5595</v>
+        <v>5598</v>
       </c>
       <c r="B28" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5662</v>
+        <v>5616</v>
       </c>
       <c r="B29" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5644</v>
+        <v>5571</v>
       </c>
       <c r="B30" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5652</v>
+        <v>5540</v>
       </c>
       <c r="B31" s="2">
-        <v>46226.30208333334</v>
+        <v>46227.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>5510</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46227.3125</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,250 +394,258 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5187</v>
+        <v>4876</v>
       </c>
       <c r="B2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5148</v>
+        <v>4833</v>
       </c>
       <c r="B3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5105</v>
+        <v>4792</v>
       </c>
       <c r="B4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5044</v>
+        <v>4624</v>
       </c>
       <c r="B5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5008</v>
+        <v>4602</v>
       </c>
       <c r="B6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4999</v>
+        <v>4596</v>
       </c>
       <c r="B7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4990</v>
+        <v>4576</v>
       </c>
       <c r="B8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5032</v>
+        <v>4545</v>
       </c>
       <c r="B9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5042</v>
+        <v>4479</v>
       </c>
       <c r="B10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5006</v>
+        <v>4444</v>
       </c>
       <c r="B11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4968</v>
+        <v>4429</v>
       </c>
       <c r="B12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4973</v>
+        <v>4417</v>
       </c>
       <c r="B13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5026</v>
+        <v>4405</v>
       </c>
       <c r="B14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5018</v>
+        <v>4392</v>
       </c>
       <c r="B15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5084</v>
+        <v>4375</v>
       </c>
       <c r="B16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5090</v>
+        <v>4364</v>
       </c>
       <c r="B17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4967</v>
+        <v>4379</v>
       </c>
       <c r="B18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4977</v>
+        <v>4367</v>
       </c>
       <c r="B19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4978</v>
+        <v>4338</v>
       </c>
       <c r="B20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5025</v>
+        <v>4273</v>
       </c>
       <c r="B21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5129</v>
+        <v>4293</v>
       </c>
       <c r="B22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5202</v>
+        <v>4268</v>
       </c>
       <c r="B23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5313</v>
+        <v>4247</v>
       </c>
       <c r="B24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5327</v>
+        <v>4219</v>
       </c>
       <c r="B25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5476</v>
+        <v>4261</v>
       </c>
       <c r="B26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5536</v>
+        <v>4214</v>
       </c>
       <c r="B27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5598</v>
+        <v>4163</v>
       </c>
       <c r="B28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5616</v>
+        <v>4147</v>
       </c>
       <c r="B29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5571</v>
+        <v>4165</v>
       </c>
       <c r="B30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5540</v>
+        <v>3958</v>
       </c>
       <c r="B31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5510</v>
+        <v>3833</v>
       </c>
       <c r="B32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>3773</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46229.32291666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,258 +394,442 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4876</v>
+        <v>5468</v>
       </c>
       <c r="B2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4833</v>
+        <v>5444</v>
       </c>
       <c r="B3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4792</v>
+        <v>5356</v>
       </c>
       <c r="B4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4624</v>
+        <v>5307</v>
       </c>
       <c r="B5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4602</v>
+        <v>5261</v>
       </c>
       <c r="B6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4596</v>
+        <v>5243</v>
       </c>
       <c r="B7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4576</v>
+        <v>5238</v>
       </c>
       <c r="B8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4545</v>
+        <v>5220</v>
       </c>
       <c r="B9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4479</v>
+        <v>5139</v>
       </c>
       <c r="B10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4444</v>
+        <v>5088</v>
       </c>
       <c r="B11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4429</v>
+        <v>5143</v>
       </c>
       <c r="B12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4417</v>
+        <v>5240</v>
       </c>
       <c r="B13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4405</v>
+        <v>5192</v>
       </c>
       <c r="B14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4392</v>
+        <v>5211</v>
       </c>
       <c r="B15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4375</v>
+        <v>5217</v>
       </c>
       <c r="B16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4364</v>
+        <v>5207</v>
       </c>
       <c r="B17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4379</v>
+        <v>5291</v>
       </c>
       <c r="B18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4367</v>
+        <v>5318</v>
       </c>
       <c r="B19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4338</v>
+        <v>5264</v>
       </c>
       <c r="B20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4273</v>
+        <v>5352</v>
       </c>
       <c r="B21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4293</v>
+        <v>5361</v>
       </c>
       <c r="B22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>4268</v>
+        <v>5424</v>
       </c>
       <c r="B23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>4247</v>
+        <v>5485</v>
       </c>
       <c r="B24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>4219</v>
+        <v>5570</v>
       </c>
       <c r="B25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>4261</v>
+        <v>5717</v>
       </c>
       <c r="B26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>4214</v>
+        <v>5755</v>
       </c>
       <c r="B27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>4163</v>
+        <v>5787</v>
       </c>
       <c r="B28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>4147</v>
+        <v>5791</v>
       </c>
       <c r="B29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>4165</v>
+        <v>5828</v>
       </c>
       <c r="B30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>3958</v>
+        <v>5840</v>
       </c>
       <c r="B31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>3833</v>
+        <v>5854</v>
       </c>
       <c r="B32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>3773</v>
+        <v>5809</v>
       </c>
       <c r="B33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>5676</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46246.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>5561</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46246.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>5470</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46246.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>5385</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46246.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>5235</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46246.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>5096</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46246.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>5039</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46246.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>4957</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46246.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>4855</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46246.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>4760</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46246.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>4773</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46246.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>4788</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46246.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>4721</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46246.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>4751</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46246.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>4758</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46246.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>4782</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46246.48958333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>4828</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46246.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>4933</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46246.51041666666</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>4946</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46246.52083333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>5031</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46246.53125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>5091</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46246.54166666666</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>5168</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46246.55208333334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>5218</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46246.5625</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,442 +394,274 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5468</v>
+        <v>4764</v>
       </c>
       <c r="B2" s="2">
-        <v>46246</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5444</v>
+        <v>4735</v>
       </c>
       <c r="B3" s="2">
-        <v>46246.01041666666</v>
+        <v>46251.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5356</v>
+        <v>4680</v>
       </c>
       <c r="B4" s="2">
-        <v>46246.02083333334</v>
+        <v>46251.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5307</v>
+        <v>4649</v>
       </c>
       <c r="B5" s="2">
-        <v>46246.03125</v>
+        <v>46251.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5261</v>
+        <v>4521</v>
       </c>
       <c r="B6" s="2">
-        <v>46246.04166666666</v>
+        <v>46251.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5243</v>
+        <v>4485</v>
       </c>
       <c r="B7" s="2">
-        <v>46246.05208333334</v>
+        <v>46251.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5238</v>
+        <v>4483</v>
       </c>
       <c r="B8" s="2">
-        <v>46246.0625</v>
+        <v>46251.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5220</v>
+        <v>4509</v>
       </c>
       <c r="B9" s="2">
-        <v>46246.07291666666</v>
+        <v>46251.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5139</v>
+        <v>4450</v>
       </c>
       <c r="B10" s="2">
-        <v>46246.08333333334</v>
+        <v>46251.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5088</v>
+        <v>4465</v>
       </c>
       <c r="B11" s="2">
-        <v>46246.09375</v>
+        <v>46251.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5143</v>
+        <v>4491</v>
       </c>
       <c r="B12" s="2">
-        <v>46246.10416666666</v>
+        <v>46251.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5240</v>
+        <v>4530</v>
       </c>
       <c r="B13" s="2">
-        <v>46246.11458333334</v>
+        <v>46251.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5192</v>
+        <v>4634</v>
       </c>
       <c r="B14" s="2">
-        <v>46246.125</v>
+        <v>46251.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5211</v>
+        <v>4630</v>
       </c>
       <c r="B15" s="2">
-        <v>46246.13541666666</v>
+        <v>46251.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5217</v>
+        <v>4649</v>
       </c>
       <c r="B16" s="2">
-        <v>46246.14583333334</v>
+        <v>46251.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5207</v>
+        <v>4661</v>
       </c>
       <c r="B17" s="2">
-        <v>46246.15625</v>
+        <v>46251.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5291</v>
+        <v>4649</v>
       </c>
       <c r="B18" s="2">
-        <v>46246.16666666666</v>
+        <v>46251.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5318</v>
+        <v>4663</v>
       </c>
       <c r="B19" s="2">
-        <v>46246.17708333334</v>
+        <v>46251.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5264</v>
+        <v>4727</v>
       </c>
       <c r="B20" s="2">
-        <v>46246.1875</v>
+        <v>46251.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5352</v>
+        <v>4739</v>
       </c>
       <c r="B21" s="2">
-        <v>46246.19791666666</v>
+        <v>46251.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5361</v>
+        <v>4814</v>
       </c>
       <c r="B22" s="2">
-        <v>46246.20833333334</v>
+        <v>46251.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5424</v>
+        <v>4884</v>
       </c>
       <c r="B23" s="2">
-        <v>46246.21875</v>
+        <v>46251.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5485</v>
+        <v>4948</v>
       </c>
       <c r="B24" s="2">
-        <v>46246.22916666666</v>
+        <v>46251.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5570</v>
+        <v>5058</v>
       </c>
       <c r="B25" s="2">
-        <v>46246.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5717</v>
+        <v>5254</v>
       </c>
       <c r="B26" s="2">
-        <v>46246.25</v>
+        <v>46251.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5755</v>
+        <v>5365</v>
       </c>
       <c r="B27" s="2">
-        <v>46246.26041666666</v>
+        <v>46251.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5787</v>
+        <v>5426</v>
       </c>
       <c r="B28" s="2">
-        <v>46246.27083333334</v>
+        <v>46251.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5791</v>
+        <v>5459</v>
       </c>
       <c r="B29" s="2">
-        <v>46246.28125</v>
+        <v>46251.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5828</v>
+        <v>5523</v>
       </c>
       <c r="B30" s="2">
-        <v>46246.29166666666</v>
+        <v>46251.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5840</v>
+        <v>5487</v>
       </c>
       <c r="B31" s="2">
-        <v>46246.30208333334</v>
+        <v>46251.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5854</v>
+        <v>5441</v>
       </c>
       <c r="B32" s="2">
-        <v>46246.3125</v>
+        <v>46251.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5809</v>
+        <v>5394</v>
       </c>
       <c r="B33" s="2">
-        <v>46246.32291666666</v>
+        <v>46251.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5676</v>
+        <v>5329</v>
       </c>
       <c r="B34" s="2">
-        <v>46246.33333333334</v>
+        <v>46251.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5561</v>
+        <v>5235</v>
       </c>
       <c r="B35" s="2">
-        <v>46246.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>5470</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46246.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>5385</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46246.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>5235</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46246.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>5096</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46246.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>5039</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46246.39583333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>4957</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46246.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>4855</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46246.41666666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>4760</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46246.42708333334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>4773</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46246.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>4788</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46246.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>4721</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46246.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>4751</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46246.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>4758</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46246.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>4782</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46246.48958333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>4828</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46246.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>4933</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46246.51041666666</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>4946</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46246.52083333334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>5031</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46246.53125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>5091</v>
-      </c>
-      <c r="B54" s="2">
-        <v>46246.54166666666</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>5168</v>
-      </c>
-      <c r="B55" s="2">
-        <v>46246.55208333334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>5218</v>
-      </c>
-      <c r="B56" s="2">
-        <v>46246.5625</v>
+        <v>46251.34375</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,274 +394,298 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4764</v>
+        <v>5243</v>
       </c>
       <c r="B2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4735</v>
+        <v>5190</v>
       </c>
       <c r="B3" s="2">
-        <v>46251.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4680</v>
+        <v>5143</v>
       </c>
       <c r="B4" s="2">
-        <v>46251.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4649</v>
+        <v>5095</v>
       </c>
       <c r="B5" s="2">
-        <v>46251.03125</v>
+        <v>46252.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4521</v>
+        <v>5060</v>
       </c>
       <c r="B6" s="2">
-        <v>46251.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4485</v>
+        <v>5031</v>
       </c>
       <c r="B7" s="2">
-        <v>46251.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4483</v>
+        <v>4996</v>
       </c>
       <c r="B8" s="2">
-        <v>46251.0625</v>
+        <v>46252.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4509</v>
+        <v>5023</v>
       </c>
       <c r="B9" s="2">
-        <v>46251.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4450</v>
+        <v>5019</v>
       </c>
       <c r="B10" s="2">
-        <v>46251.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4465</v>
+        <v>5104</v>
       </c>
       <c r="B11" s="2">
-        <v>46251.09375</v>
+        <v>46252.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4491</v>
+        <v>5201</v>
       </c>
       <c r="B12" s="2">
-        <v>46251.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4530</v>
+        <v>5234</v>
       </c>
       <c r="B13" s="2">
-        <v>46251.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4634</v>
+        <v>5240</v>
       </c>
       <c r="B14" s="2">
-        <v>46251.125</v>
+        <v>46252.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4630</v>
+        <v>5235</v>
       </c>
       <c r="B15" s="2">
-        <v>46251.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4649</v>
+        <v>5228</v>
       </c>
       <c r="B16" s="2">
-        <v>46251.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4661</v>
+        <v>5231</v>
       </c>
       <c r="B17" s="2">
-        <v>46251.15625</v>
+        <v>46252.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4649</v>
+        <v>5261</v>
       </c>
       <c r="B18" s="2">
-        <v>46251.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4663</v>
+        <v>5230</v>
       </c>
       <c r="B19" s="2">
-        <v>46251.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4727</v>
+        <v>5244</v>
       </c>
       <c r="B20" s="2">
-        <v>46251.1875</v>
+        <v>46252.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4739</v>
+        <v>5248</v>
       </c>
       <c r="B21" s="2">
-        <v>46251.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4814</v>
+        <v>5220</v>
       </c>
       <c r="B22" s="2">
-        <v>46251.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>4884</v>
+        <v>5292</v>
       </c>
       <c r="B23" s="2">
-        <v>46251.21875</v>
+        <v>46252.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>4948</v>
+        <v>5389</v>
       </c>
       <c r="B24" s="2">
-        <v>46251.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5058</v>
+        <v>5478</v>
       </c>
       <c r="B25" s="2">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5254</v>
+        <v>5623</v>
       </c>
       <c r="B26" s="2">
-        <v>46251.25</v>
+        <v>46252.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5365</v>
+        <v>5750</v>
       </c>
       <c r="B27" s="2">
-        <v>46251.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5426</v>
+        <v>5825</v>
       </c>
       <c r="B28" s="2">
-        <v>46251.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5459</v>
+        <v>5899</v>
       </c>
       <c r="B29" s="2">
-        <v>46251.28125</v>
+        <v>46252.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5523</v>
+        <v>5983</v>
       </c>
       <c r="B30" s="2">
-        <v>46251.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5487</v>
+        <v>5990</v>
       </c>
       <c r="B31" s="2">
-        <v>46251.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5441</v>
+        <v>5973</v>
       </c>
       <c r="B32" s="2">
-        <v>46251.3125</v>
+        <v>46252.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5394</v>
+        <v>5926</v>
       </c>
       <c r="B33" s="2">
-        <v>46251.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5329</v>
+        <v>5910</v>
       </c>
       <c r="B34" s="2">
-        <v>46251.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5235</v>
+        <v>6029</v>
       </c>
       <c r="B35" s="2">
-        <v>46251.34375</v>
+        <v>46252.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>5857</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46252.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>5761</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46252.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>5664</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46252.375</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,298 +394,242 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5243</v>
+        <v>5493</v>
       </c>
       <c r="B2" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5190</v>
+        <v>5412</v>
       </c>
       <c r="B3" s="2">
-        <v>46252.01041666666</v>
+        <v>46259.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5143</v>
+        <v>5442</v>
       </c>
       <c r="B4" s="2">
-        <v>46252.02083333334</v>
+        <v>46259.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5095</v>
+        <v>5373</v>
       </c>
       <c r="B5" s="2">
-        <v>46252.03125</v>
+        <v>46259.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5060</v>
+        <v>5317</v>
       </c>
       <c r="B6" s="2">
-        <v>46252.04166666666</v>
+        <v>46259.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5031</v>
+        <v>5316</v>
       </c>
       <c r="B7" s="2">
-        <v>46252.05208333334</v>
+        <v>46259.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4996</v>
+        <v>5308</v>
       </c>
       <c r="B8" s="2">
-        <v>46252.0625</v>
+        <v>46259.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5023</v>
+        <v>5274</v>
       </c>
       <c r="B9" s="2">
-        <v>46252.07291666666</v>
+        <v>46259.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5019</v>
+        <v>5283</v>
       </c>
       <c r="B10" s="2">
-        <v>46252.08333333334</v>
+        <v>46259.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5104</v>
+        <v>5302</v>
       </c>
       <c r="B11" s="2">
-        <v>46252.09375</v>
+        <v>46259.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5201</v>
+        <v>5288</v>
       </c>
       <c r="B12" s="2">
-        <v>46252.10416666666</v>
+        <v>46259.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5234</v>
+        <v>5309</v>
       </c>
       <c r="B13" s="2">
-        <v>46252.11458333334</v>
+        <v>46259.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5240</v>
+        <v>5294</v>
       </c>
       <c r="B14" s="2">
-        <v>46252.125</v>
+        <v>46259.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5235</v>
+        <v>5332</v>
       </c>
       <c r="B15" s="2">
-        <v>46252.13541666666</v>
+        <v>46259.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5228</v>
+        <v>5393</v>
       </c>
       <c r="B16" s="2">
-        <v>46252.14583333334</v>
+        <v>46259.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5231</v>
+        <v>5281</v>
       </c>
       <c r="B17" s="2">
-        <v>46252.15625</v>
+        <v>46259.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5261</v>
+        <v>5360</v>
       </c>
       <c r="B18" s="2">
-        <v>46252.16666666666</v>
+        <v>46259.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5230</v>
+        <v>5296</v>
       </c>
       <c r="B19" s="2">
-        <v>46252.17708333334</v>
+        <v>46259.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5244</v>
+        <v>5428</v>
       </c>
       <c r="B20" s="2">
-        <v>46252.1875</v>
+        <v>46259.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5248</v>
+        <v>5465</v>
       </c>
       <c r="B21" s="2">
-        <v>46252.19791666666</v>
+        <v>46259.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5220</v>
+        <v>5530</v>
       </c>
       <c r="B22" s="2">
-        <v>46252.20833333334</v>
+        <v>46259.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5292</v>
+        <v>5501</v>
       </c>
       <c r="B23" s="2">
-        <v>46252.21875</v>
+        <v>46259.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5389</v>
+        <v>5563</v>
       </c>
       <c r="B24" s="2">
-        <v>46252.22916666666</v>
+        <v>46259.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5478</v>
+        <v>5642</v>
       </c>
       <c r="B25" s="2">
-        <v>46252.23958333334</v>
+        <v>46259.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5623</v>
+        <v>5757</v>
       </c>
       <c r="B26" s="2">
-        <v>46252.25</v>
+        <v>46259.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5750</v>
+        <v>5815</v>
       </c>
       <c r="B27" s="2">
-        <v>46252.26041666666</v>
+        <v>46259.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5825</v>
+        <v>5872</v>
       </c>
       <c r="B28" s="2">
-        <v>46252.27083333334</v>
+        <v>46259.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5899</v>
+        <v>5974</v>
       </c>
       <c r="B29" s="2">
-        <v>46252.28125</v>
+        <v>46259.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5983</v>
+        <v>5950</v>
       </c>
       <c r="B30" s="2">
-        <v>46252.29166666666</v>
+        <v>46259.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5990</v>
+        <v>5932</v>
       </c>
       <c r="B31" s="2">
-        <v>46252.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>5973</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46252.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>5926</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46252.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>5910</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46252.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>6029</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46252.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>5857</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46252.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>5761</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46252.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>5664</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46252.375</v>
+        <v>46259.30208333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,242 +394,402 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5493</v>
+        <v>5138</v>
       </c>
       <c r="B2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5412</v>
+        <v>5124</v>
       </c>
       <c r="B3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5442</v>
+        <v>5072</v>
       </c>
       <c r="B4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5373</v>
+        <v>5007</v>
       </c>
       <c r="B5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5317</v>
+        <v>4918</v>
       </c>
       <c r="B6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5316</v>
+        <v>4920</v>
       </c>
       <c r="B7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5308</v>
+        <v>4865</v>
       </c>
       <c r="B8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5274</v>
+        <v>4903</v>
       </c>
       <c r="B9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5283</v>
+        <v>4917</v>
       </c>
       <c r="B10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5302</v>
+        <v>4918</v>
       </c>
       <c r="B11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5288</v>
+        <v>4911</v>
       </c>
       <c r="B12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5309</v>
+        <v>4923</v>
       </c>
       <c r="B13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5294</v>
+        <v>4948</v>
       </c>
       <c r="B14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5332</v>
+        <v>4964</v>
       </c>
       <c r="B15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5393</v>
+        <v>5013</v>
       </c>
       <c r="B16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5281</v>
+        <v>5011</v>
       </c>
       <c r="B17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5360</v>
+        <v>5036</v>
       </c>
       <c r="B18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5296</v>
+        <v>5099</v>
       </c>
       <c r="B19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5428</v>
+        <v>5121</v>
       </c>
       <c r="B20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5465</v>
+        <v>5183</v>
       </c>
       <c r="B21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5530</v>
+        <v>5202</v>
       </c>
       <c r="B22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5501</v>
+        <v>5247</v>
       </c>
       <c r="B23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5563</v>
+        <v>5262</v>
       </c>
       <c r="B24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5642</v>
+        <v>5364</v>
       </c>
       <c r="B25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5757</v>
+        <v>5603</v>
       </c>
       <c r="B26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5815</v>
+        <v>5706</v>
       </c>
       <c r="B27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5872</v>
+        <v>5731</v>
       </c>
       <c r="B28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5974</v>
+        <v>5783</v>
       </c>
       <c r="B29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5950</v>
+        <v>5845</v>
       </c>
       <c r="B30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5932</v>
+        <v>5820</v>
       </c>
       <c r="B31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>5775</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46262.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>5667</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46262.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>5555</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46262.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>5546</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46262.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>5392</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46262.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>5212</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46262.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>5121</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46262.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>5003</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46262.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>4844</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46262.39583333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>4820</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46262.40625</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>4663</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46262.41666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>4501</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46262.42708333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>4493</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46262.4375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>4432</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46262.44791666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>4362</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46262.45833333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>4467</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46262.46875</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>4519</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46262.47916666666</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>4537</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46262.48958333334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>4539</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46262.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>4556</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46262.51041666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,402 +394,370 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5138</v>
+        <v>5428</v>
       </c>
       <c r="B2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5124</v>
+        <v>5388</v>
       </c>
       <c r="B3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5072</v>
+        <v>5284</v>
       </c>
       <c r="B4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5007</v>
+        <v>5287</v>
       </c>
       <c r="B5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4918</v>
+        <v>5213</v>
       </c>
       <c r="B6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4920</v>
+        <v>5274</v>
       </c>
       <c r="B7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4865</v>
+        <v>5284</v>
       </c>
       <c r="B8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4903</v>
+        <v>5249</v>
       </c>
       <c r="B9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4917</v>
+        <v>5376</v>
       </c>
       <c r="B10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4918</v>
+        <v>5356</v>
       </c>
       <c r="B11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4911</v>
+        <v>5344</v>
       </c>
       <c r="B12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4923</v>
+        <v>5352</v>
       </c>
       <c r="B13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4948</v>
+        <v>5400</v>
       </c>
       <c r="B14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4964</v>
+        <v>5421</v>
       </c>
       <c r="B15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5013</v>
+        <v>5383</v>
       </c>
       <c r="B16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5011</v>
+        <v>5396</v>
       </c>
       <c r="B17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5036</v>
+        <v>5418</v>
       </c>
       <c r="B18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5099</v>
+        <v>5408</v>
       </c>
       <c r="B19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5121</v>
+        <v>5384</v>
       </c>
       <c r="B20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5183</v>
+        <v>5415</v>
       </c>
       <c r="B21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5202</v>
+        <v>5613</v>
       </c>
       <c r="B22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5247</v>
+        <v>5633</v>
       </c>
       <c r="B23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5262</v>
+        <v>5634</v>
       </c>
       <c r="B24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5364</v>
+        <v>5698</v>
       </c>
       <c r="B25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5603</v>
+        <v>5880</v>
       </c>
       <c r="B26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5706</v>
+        <v>5954</v>
       </c>
       <c r="B27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5731</v>
+        <v>6024</v>
       </c>
       <c r="B28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5783</v>
+        <v>6067</v>
       </c>
       <c r="B29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5845</v>
+        <v>6057</v>
       </c>
       <c r="B30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>5820</v>
+        <v>6051</v>
       </c>
       <c r="B31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5775</v>
+        <v>6032</v>
       </c>
       <c r="B32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5667</v>
+        <v>6008</v>
       </c>
       <c r="B33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5555</v>
+        <v>5780</v>
       </c>
       <c r="B34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5546</v>
+        <v>5781</v>
       </c>
       <c r="B35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5392</v>
+        <v>5648</v>
       </c>
       <c r="B36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5212</v>
+        <v>5443</v>
       </c>
       <c r="B37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>5121</v>
+        <v>5280</v>
       </c>
       <c r="B38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>5003</v>
+        <v>5062</v>
       </c>
       <c r="B39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>4844</v>
+        <v>4932</v>
       </c>
       <c r="B40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>4820</v>
+        <v>4837</v>
       </c>
       <c r="B41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>4663</v>
+        <v>4736</v>
       </c>
       <c r="B42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>4501</v>
+        <v>4789</v>
       </c>
       <c r="B43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>4493</v>
+        <v>4791</v>
       </c>
       <c r="B44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>4432</v>
+        <v>4642</v>
       </c>
       <c r="B45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>4362</v>
+        <v>4752</v>
       </c>
       <c r="B46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>4467</v>
+        <v>4652</v>
       </c>
       <c r="B47" s="2">
-        <v>46262.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>4519</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46262.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>4537</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46262.48958333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>4539</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46262.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>4556</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46262.51041666666</v>
+        <v>46269.46875</v>
       </c>
     </row>
   </sheetData>
